--- a/lw3Tweets.xlsx
+++ b/lw3Tweets.xlsx
@@ -28,7 +28,7 @@
     <t>DaysOfCoding</t>
   </si>
   <si>
-    <t>(2022, 12, 25)</t>
+    <t>(2022, 12, 29)</t>
   </si>
   <si>
     <t>karan_pargal</t>
@@ -490,7 +490,7 @@
         <v>13</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -504,7 +504,7 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -518,7 +518,7 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -532,7 +532,7 @@
         <v>16</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -546,7 +546,7 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -560,7 +560,7 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -574,7 +574,7 @@
         <v>19</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -588,7 +588,7 @@
         <v>20</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/lw3Tweets.xlsx
+++ b/lw3Tweets.xlsx
@@ -31,52 +31,44 @@
     <t>(2022, 12, 29)</t>
   </si>
   <si>
+    <t>Ibrahim_ether</t>
+  </si>
+  <si>
+    <t>rahul3526</t>
+  </si>
+  <si>
+    <t>TiwariAnkitb</t>
+  </si>
+  <si>
+    <t>0xCylax</t>
+  </si>
+  <si>
+    <t>PandeyAshwini9</t>
+  </si>
+  <si>
+    <t>khizraashaikh</t>
+  </si>
+  <si>
+    <t>zakirali_05</t>
+  </si>
+  <si>
     <t>karan_pargal</t>
   </si>
   <si>
-    <t>TiwariAnkitb</t>
-  </si>
-  <si>
-    <t>PandeyAshwini9</t>
-  </si>
-  <si>
-    <t>rahul3526</t>
-  </si>
-  <si>
-    <t>0xCylax</t>
-  </si>
-  <si>
-    <t>khizraashaikh</t>
-  </si>
-  <si>
-    <t>zakirali_05</t>
-  </si>
-  <si>
-    <t>Ibrahim_ether</t>
-  </si>
-  <si>
-    <t>Day 1/100 of #100DaysOfCode 
-Learned how to connect frontend with smart contracts and finished whitelisting dApp.
-Hosted at:
-https://t.co/RnrOK28Gn3
-Thanks to @LearnWeb3DAO for the brilliant course.</t>
+    <t>Day 5 of #100DaysOfCode. I built a whitelist dapp with @LearnWeb3DAO that allows selected addresses to participate in Crypto Devs NFT collection presale. I learnt new @solidity_lang syntax in the process.
+The project is hosted on:
+https://t.co/2QHJJdGv7I https://t.co/2ZbsOGGRja</t>
+  </si>
+  <si>
+    <t>Round 2. 
+Day 5 of #100DaysOfCode.
+Learned about the basic functionality of ERC 1155 standard from the blog of @Aayush_gupta_ji on hashnode which was uploaded to @LearnWeb3DAO .</t>
   </si>
   <si>
     <t>Day25 of #100daysofcode with @Ashwini86226992  from @LearnWeb3DAO.
 Today i learnt about React and Next.js basics from sophomore level .
 #Web3 
 #web3community</t>
-  </si>
-  <si>
-    <t>Day25 of #100daysofcode with @TiwariAnkitb  from @LearnWeb3DAO.
-Today i learnt about React and Next.js basics from sophomore level .
-#Web3 
-#web3community</t>
-  </si>
-  <si>
-    <t>Round 2. 
-Day 5 of #100DaysOfCode.
-Learned about the basic functionality of ERC 1155 standard from the blog of @Aayush_gupta_ji on hashnode which was uploaded to @LearnWeb3DAO .</t>
   </si>
   <si>
     <t>Day 2 of #100DaysOfCode 
@@ -85,6 +77,12 @@
 - learned about React Routing 
 - Added Routing to SuperMeal app, will deploy it soon ; 
 video 🧵⬇ https://t.co/TJHcGzTRzP</t>
+  </si>
+  <si>
+    <t>Day25 of #100daysofcode with @TiwariAnkitb  from @LearnWeb3DAO.
+Today i learnt about React and Next.js basics from sophomore level .
+#Web3 
+#web3community</t>
   </si>
   <si>
     <t>How To Become A Web3 Developer by @AkashShyam11 https://t.co/rYVKzKhKL0 
@@ -102,9 +100,11 @@
 learning from @LearnWeb3DAO</t>
   </si>
   <si>
-    <t>Day 5 of #100DaysOfCode. I built a whitelist dapp with @LearnWeb3DAO that allows selected addresses to participate in Crypto Devs NFT collection presale. I learnt new @solidity_lang syntax in the process.
-The project is hosted on:
-https://t.co/2QHJJdGv7I https://t.co/2ZbsOGGRja</t>
+    <t>Day 1/100 of #100DaysOfCode 
+Learned how to connect frontend with smart contracts and finished whitelisting dApp.
+Hosted at:
+https://t.co/RnrOK28Gn3
+Thanks to @LearnWeb3DAO for the brilliant course.</t>
   </si>
 </sst>
 </file>
@@ -490,7 +490,7 @@
         <v>13</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -504,7 +504,7 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -518,7 +518,7 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -532,7 +532,7 @@
         <v>16</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -588,7 +588,7 @@
         <v>20</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/lw3Tweets.xlsx
+++ b/lw3Tweets.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>Date Created</t>
   </si>
@@ -28,83 +28,27 @@
     <t>DaysOfCoding</t>
   </si>
   <si>
-    <t>(2022, 12, 29)</t>
-  </si>
-  <si>
-    <t>Ibrahim_ether</t>
-  </si>
-  <si>
-    <t>rahul3526</t>
+    <t>(2022, 12, 30)</t>
+  </si>
+  <si>
+    <t>PandeyAshwini9</t>
   </si>
   <si>
     <t>TiwariAnkitb</t>
   </si>
   <si>
-    <t>0xCylax</t>
-  </si>
-  <si>
-    <t>PandeyAshwini9</t>
-  </si>
-  <si>
-    <t>khizraashaikh</t>
-  </si>
-  <si>
-    <t>zakirali_05</t>
-  </si>
-  <si>
-    <t>karan_pargal</t>
-  </si>
-  <si>
-    <t>Day 5 of #100DaysOfCode. I built a whitelist dapp with @LearnWeb3DAO that allows selected addresses to participate in Crypto Devs NFT collection presale. I learnt new @solidity_lang syntax in the process.
-The project is hosted on:
-https://t.co/2QHJJdGv7I https://t.co/2ZbsOGGRja</t>
-  </si>
-  <si>
-    <t>Round 2. 
-Day 5 of #100DaysOfCode.
-Learned about the basic functionality of ERC 1155 standard from the blog of @Aayush_gupta_ji on hashnode which was uploaded to @LearnWeb3DAO .</t>
-  </si>
-  <si>
-    <t>Day25 of #100daysofcode with @Ashwini86226992  from @LearnWeb3DAO.
-Today i learnt about React and Next.js basics from sophomore level .
+    <t>Day 44 of #100DaysOfCode with @TiwariAnkitb by @LearnWeb3DAO .
+Build your own fully on-chain DAO to invest in NFTs✅
+check it...
+https://t.co/HgLNVUNvp7
+#Web3 
+#web3community https://t.co/R0fJjQ9caG</t>
+  </si>
+  <si>
+    <t>Day 45 of #100DaysOfCode with @PandeyAshwini9 from @LearnWeb3DAO.
+Completed 85% on the sophomore level and achieving more...
 #Web3 
 #web3community</t>
-  </si>
-  <si>
-    <t>Day 2 of #100DaysOfCode 
-- reviewed blockchain basics on @LearnWeb3DAO (completed 50% of freshmen track)  ✌🏼
-- learning Java 💭
-- learned about React Routing 
-- Added Routing to SuperMeal app, will deploy it soon ; 
-video 🧵⬇ https://t.co/TJHcGzTRzP</t>
-  </si>
-  <si>
-    <t>Day25 of #100daysofcode with @TiwariAnkitb  from @LearnWeb3DAO.
-Today i learnt about React and Next.js basics from sophomore level .
-#Web3 
-#web3community</t>
-  </si>
-  <si>
-    <t>How To Become A Web3 Developer by @AkashShyam11 https://t.co/rYVKzKhKL0 
-After reading this article, I'm crystal clear about Web3 (you can understand)
-And I'm starting my Web3 Journey by following @LearnWeb3DAO Freshman-Track✨
-@Medium #Web3 #web3community #100DaysOfCode #day21</t>
-  </si>
-  <si>
-    <t>Day:9 #100daysofcode most productive day...
-- Basic of Blockchain
-- What are wallets
-- what is etherium
-- introduction to solidity
-- introduction to ether.js 
-learning from @LearnWeb3DAO</t>
-  </si>
-  <si>
-    <t>Day 1/100 of #100DaysOfCode 
-Learned how to connect frontend with smart contracts and finished whitelisting dApp.
-Hosted at:
-https://t.co/RnrOK28Gn3
-Thanks to @LearnWeb3DAO for the brilliant course.</t>
   </si>
 </sst>
 </file>
@@ -462,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -487,10 +431,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D2">
-        <v>111</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -501,94 +445,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/lw3Tweets.xlsx
+++ b/lw3Tweets.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Date Created</t>
   </si>
@@ -28,27 +28,54 @@
     <t>DaysOfCoding</t>
   </si>
   <si>
-    <t>(2022, 12, 30)</t>
+    <t>(2023, 1, 1)</t>
+  </si>
+  <si>
+    <t>(2022, 12, 31)</t>
+  </si>
+  <si>
+    <t>heheh</t>
+  </si>
+  <si>
+    <t>TiwariAnkitb</t>
+  </si>
+  <si>
+    <t>rahul3526</t>
   </si>
   <si>
     <t>PandeyAshwini9</t>
   </si>
   <si>
-    <t>TiwariAnkitb</t>
-  </si>
-  <si>
-    <t>Day 44 of #100DaysOfCode with @TiwariAnkitb by @LearnWeb3DAO .
-Build your own fully on-chain DAO to invest in NFTs✅
-check it...
-https://t.co/HgLNVUNvp7
-#Web3 
-#web3community https://t.co/R0fJjQ9caG</t>
-  </si>
-  <si>
-    <t>Day 45 of #100DaysOfCode with @PandeyAshwini9 from @LearnWeb3DAO.
-Completed 85% on the sophomore level and achieving more...
-#Web3 
-#web3community</t>
+    <t>Day 47 of #100DaysOfCode with @TiwariAnkitb from @LearnWeb3DAO.
+In progress....
+Build your own Decentraized exchange like Uniswap.
+Solidity code ✅
+Ether.js✅
+Hardhat ✅
+NextJs❌
+Excited for tomorrow...
+#Web3
+#Blockchain
+#100daysofcodingchallenge</t>
+  </si>
+  <si>
+    <t>Day 47 of #100DaysOfCode with @PandeyAshwini9 from @LearnWeb3DAO.
+In progress....
+Build your own Decentraized exchange like Uniswap.
+Solidity code ✅
+Ether.js✅
+Hardhat ✅
+NextJs❌
+Excited for tomorrow...
+#Web3
+#Blockchain
+#100daysofcodingchallenge</t>
+  </si>
+  <si>
+    <t>Round 2.
+Day 10 of #100DaysOfCode .
+Made a video on How to get started with rainbow kit. Also gave a easy solution to the hydration error problem Had been facing it for so long. Check out the video in comments below. I would like to thank @LearnWeb3DAO  
+https://t.co/rQ2h5tDpsQ</t>
   </si>
 </sst>
 </file>
@@ -406,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -428,13 +455,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -442,12 +469,40 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="D3">
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5">
         <v>1</v>
       </c>
     </row>

--- a/lw3Tweets.xlsx
+++ b/lw3Tweets.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Date Created</t>
   </si>
@@ -25,64 +25,86 @@
     <t>Tweets</t>
   </si>
   <si>
+    <t>Link</t>
+  </si>
+  <si>
     <t>DaysOfCoding</t>
   </si>
   <si>
-    <t>(2023, 1, 1)</t>
-  </si>
-  <si>
-    <t>(2022, 12, 31)</t>
-  </si>
-  <si>
-    <t>heheh</t>
-  </si>
-  <si>
-    <t>TiwariAnkitb</t>
-  </si>
-  <si>
-    <t>rahul3526</t>
-  </si>
-  <si>
-    <t>PandeyAshwini9</t>
-  </si>
-  <si>
-    <t>Day 47 of #100DaysOfCode with @TiwariAnkitb from @LearnWeb3DAO.
-In progress....
-Build your own Decentraized exchange like Uniswap.
-Solidity code ✅
-Ether.js✅
-Hardhat ✅
-NextJs❌
-Excited for tomorrow...
-#Web3
-#Blockchain
-#100daysofcodingchallenge</t>
-  </si>
-  <si>
-    <t>Day 47 of #100DaysOfCode with @PandeyAshwini9 from @LearnWeb3DAO.
-In progress....
-Build your own Decentraized exchange like Uniswap.
-Solidity code ✅
-Ether.js✅
-Hardhat ✅
-NextJs❌
-Excited for tomorrow...
-#Web3
-#Blockchain
-#100daysofcodingchallenge</t>
-  </si>
-  <si>
-    <t>Round 2.
-Day 10 of #100DaysOfCode .
-Made a video on How to get started with rainbow kit. Also gave a easy solution to the hydration error problem Had been facing it for so long. Check out the video in comments below. I would like to thank @LearnWeb3DAO  
-https://t.co/rQ2h5tDpsQ</t>
+    <t>(2023, 1, 5)</t>
+  </si>
+  <si>
+    <t>Syvelline</t>
+  </si>
+  <si>
+    <t>0xCylax</t>
+  </si>
+  <si>
+    <t>ArshiaZojaji</t>
+  </si>
+  <si>
+    <t>yc_crypto</t>
+  </si>
+  <si>
+    <t>cjski_web3</t>
+  </si>
+  <si>
+    <t>Day- 38 of #100DaysOfCode 
+✅Spent reading about Ethereum and Bitcoin in-depth and continued freshman track @LearnWeb3DAO 
+✅Completed lesson 1 of solidity @CryptoZombiesHQ 
+Most productive day of a challenge since I picked it again
+#100daysofcodechallenge #100daysofcoding https://t.co/seWOV7BYgr</t>
+  </si>
+  <si>
+    <t>Day 18 of #100DaysOfCode
+- solved few problems using linear search algorithm
+- almost completed building shopping app project using React
+- learned more about hardhat on @AlchemyLearn (60% of week 4 ✅)
+- completed 30% of sophomore track🏕 on @LearnWeb3DAO https://t.co/5lShrbLEy5</t>
+  </si>
+  <si>
+    <t>Day 4⃣ of journey to learn #smartcontracts 🥳
+I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community! 💻
+We'll be focusing on Web3 development for 100 days!
+Join us here👇
+🔗https://t.co/hoEtohzV5Z
+#100DaysofCodeLW3 https://t.co/8vBrLGM7iI</t>
+  </si>
+  <si>
+    <t>Planning to start #100daysofcode once again. will document my journey here and @LearnWeb3DAO and @scdevstr discord channels. 
+I will plan my calendar this weekend and starting on monday.
+#100DAYSOFCODELW3</t>
+  </si>
+  <si>
+    <t>Alright champs, here's what we are going to do together as web3 community 😎
+As it was officially announced in @LearnWeb3DAO discord, on 9th of January we are going to start community driven #100DaysOfCode challenge. 
+@haardikkk
+@Haezurath
+@KhanAbbas201
+@LarryCutts6
+👇</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Syvelline/status/1611059503746928640</t>
+  </si>
+  <si>
+    <t>https://twitter.com/0xCylax/status/1611030272782499840</t>
+  </si>
+  <si>
+    <t>https://twitter.com/ArshiaZojaji/status/1611032640710389760</t>
+  </si>
+  <si>
+    <t>https://twitter.com/yc_crypto/status/1610929639576293376</t>
+  </si>
+  <si>
+    <t>https://twitter.com/cjski_web3/status/1610812225807056896</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,6 +119,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -131,16 +160,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -433,10 +468,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -449,36 +484,45 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -486,27 +530,57 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="D5">
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1"/>
+    <hyperlink ref="D3" r:id="rId2"/>
+    <hyperlink ref="D4" r:id="rId3"/>
+    <hyperlink ref="D5" r:id="rId4"/>
+    <hyperlink ref="D6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/lw3Tweets.xlsx
+++ b/lw3Tweets.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
   <si>
     <t>Date Created</t>
   </si>
@@ -31,22 +31,63 @@
     <t>DaysOfCoding</t>
   </si>
   <si>
+    <t>(2023, 1, 6)</t>
+  </si>
+  <si>
     <t>(2023, 1, 5)</t>
   </si>
   <si>
+    <t>(2023, 1, 7)</t>
+  </si>
+  <si>
+    <t>ArshiaZojaji</t>
+  </si>
+  <si>
+    <t>0xCylax</t>
+  </si>
+  <si>
     <t>Syvelline</t>
   </si>
   <si>
-    <t>0xCylax</t>
-  </si>
-  <si>
-    <t>ArshiaZojaji</t>
-  </si>
-  <si>
     <t>yc_crypto</t>
   </si>
   <si>
     <t>cjski_web3</t>
+  </si>
+  <si>
+    <t>web3Learning2</t>
+  </si>
+  <si>
+    <t>Maitrayeedas9</t>
+  </si>
+  <si>
+    <t>a20zCrypto</t>
+  </si>
+  <si>
+    <t>0xLesanders</t>
+  </si>
+  <si>
+    <t>rav3kid</t>
+  </si>
+  <si>
+    <t>Justacanuk81</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 5⃣ of #100daysofcode w/ @LearnWeb3DAO
+JavaScript are fundamentals are finished today, wow that was big. 🥳🔥
+worked on:
+1. Objects
+2. Loops
+3. Functions
+#100DaysofCodeLW3 #javascript https://t.co/qdGzkLVdMr</t>
+  </si>
+  <si>
+    <t>Day 19 of #100DaysOfCode 
+- learned about binary search algorithm 
+- learned about receive &amp;amp; revert functions, function modifiers on AU (w4 - 70%) 
+- 'working of Proof of Stake' on @LearnWeb3DAO 
+- added media queries &amp;amp; products page in shopping app project https://t.co/vfAZf7LqYL</t>
   </si>
   <si>
     <t>Day- 38 of #100DaysOfCode 
@@ -54,21 +95,6 @@
 ✅Completed lesson 1 of solidity @CryptoZombiesHQ 
 Most productive day of a challenge since I picked it again
 #100daysofcodechallenge #100daysofcoding https://t.co/seWOV7BYgr</t>
-  </si>
-  <si>
-    <t>Day 18 of #100DaysOfCode
-- solved few problems using linear search algorithm
-- almost completed building shopping app project using React
-- learned more about hardhat on @AlchemyLearn (60% of week 4 ✅)
-- completed 30% of sophomore track🏕 on @LearnWeb3DAO https://t.co/5lShrbLEy5</t>
-  </si>
-  <si>
-    <t>Day 4⃣ of journey to learn #smartcontracts 🥳
-I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community! 💻
-We'll be focusing on Web3 development for 100 days!
-Join us here👇
-🔗https://t.co/hoEtohzV5Z
-#100DaysofCodeLW3 https://t.co/8vBrLGM7iI</t>
   </si>
   <si>
     <t>Planning to start #100daysofcode once again. will document my journey here and @LearnWeb3DAO and @scdevstr discord channels. 
@@ -85,19 +111,79 @@
 👇</t>
   </si>
   <si>
+    <t>I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community! 💻
+We'll be focusing on Web3 development for 100 days!
+Join us here👇
+https://t.co/WmBIxayEod
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community! 💻
+I’ll be focusing on Web3 development for 100 days!
+Starting from January 9th.</t>
+  </si>
+  <si>
+    <t>Wanted to get an early head start...
+Day 1 of #100DaysOfCode with @LearnWeb3DAO
+-Research on effective GitHub use
+-JavaScript Rock, Paper, Scissors program focusing on different JS function syntax
+#100DaysofCodeLW3
+#Web3
+#web3community 
+@Codecademy</t>
+  </si>
+  <si>
+    <t>Day 4-5 | #100DaysOfWeb3 &amp;amp; #100DaysOfCode 
+• Finished Solidity Course 
+I will work on my final project for practicum.
+• Also will follow Freshman level on @LearnWeb3DAO https://t.co/A6aYqEjLZn</t>
+  </si>
+  <si>
+    <t>I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community! 💻
+We'll be focusing on Web3 development for 100 days!
+Join us here👇
+https://t.co/SyVMQByYkK
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community! 💻
+We'll be focusing on Web3 development for 100 days!
+Join us here👇
+https://t.co/9epZdiLLFL
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>https://twitter.com/ArshiaZojaji/status/1611393669428350979</t>
+  </si>
+  <si>
+    <t>https://twitter.com/0xCylax/status/1611394241904926721</t>
+  </si>
+  <si>
     <t>https://twitter.com/Syvelline/status/1611059503746928640</t>
   </si>
   <si>
-    <t>https://twitter.com/0xCylax/status/1611030272782499840</t>
-  </si>
-  <si>
-    <t>https://twitter.com/ArshiaZojaji/status/1611032640710389760</t>
-  </si>
-  <si>
     <t>https://twitter.com/yc_crypto/status/1610929639576293376</t>
   </si>
   <si>
     <t>https://twitter.com/cjski_web3/status/1610812225807056896</t>
+  </si>
+  <si>
+    <t>https://twitter.com/web3Learning2/status/1611323420074975232</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Maitrayeedas9/status/1611314578625028096</t>
+  </si>
+  <si>
+    <t>https://twitter.com/a20zCrypto/status/1611478248202047488</t>
+  </si>
+  <si>
+    <t>https://twitter.com/0xLesanders/status/1611705616476831744</t>
+  </si>
+  <si>
+    <t>https://twitter.com/rav3kid/status/1611626477900165123</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Justacanuk81/status/1611756569502552070</t>
   </si>
 </sst>
 </file>
@@ -468,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -493,16 +579,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -510,30 +596,30 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -541,16 +627,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -558,18 +644,120 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6">
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12">
         <v>1</v>
       </c>
     </row>
@@ -580,6 +768,12 @@
     <hyperlink ref="D4" r:id="rId3"/>
     <hyperlink ref="D5" r:id="rId4"/>
     <hyperlink ref="D6" r:id="rId5"/>
+    <hyperlink ref="D7" r:id="rId6"/>
+    <hyperlink ref="D8" r:id="rId7"/>
+    <hyperlink ref="D9" r:id="rId8"/>
+    <hyperlink ref="D10" r:id="rId9"/>
+    <hyperlink ref="D11" r:id="rId10"/>
+    <hyperlink ref="D12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/lw3Tweets.xlsx
+++ b/lw3Tweets.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="247">
   <si>
     <t>Date Created</t>
   </si>
@@ -31,159 +31,1027 @@
     <t>DaysOfCoding</t>
   </si>
   <si>
-    <t>(2023, 1, 6)</t>
-  </si>
-  <si>
-    <t>(2023, 1, 5)</t>
-  </si>
-  <si>
-    <t>(2023, 1, 7)</t>
+    <t>(2023, 1, 15)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 14)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 13)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 12)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 11)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 10)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 9)</t>
+  </si>
+  <si>
+    <t>AamirUsmani1552</t>
+  </si>
+  <si>
+    <t>a20zCrypto</t>
+  </si>
+  <si>
+    <t>nandagopan__</t>
+  </si>
+  <si>
+    <t>nithinchandranp</t>
+  </si>
+  <si>
+    <t>2xprathamesh</t>
+  </si>
+  <si>
+    <t>ChaffieRN</t>
+  </si>
+  <si>
+    <t>HanabiPlug</t>
+  </si>
+  <si>
+    <t>Maitrayeedas9</t>
+  </si>
+  <si>
+    <t>dazkool69</t>
+  </si>
+  <si>
+    <t>manoharsspace</t>
+  </si>
+  <si>
+    <t>kushagrasarathe</t>
+  </si>
+  <si>
+    <t>RitikkAgarwalll</t>
+  </si>
+  <si>
+    <t>blagoichelovek</t>
+  </si>
+  <si>
+    <t>Jbusta2103</t>
+  </si>
+  <si>
+    <t>_0x416B68696C_</t>
+  </si>
+  <si>
+    <t>karthik___gk</t>
+  </si>
+  <si>
+    <t>yc_crypto</t>
+  </si>
+  <si>
+    <t>vundnido</t>
+  </si>
+  <si>
+    <t>seamlesslyjj</t>
+  </si>
+  <si>
+    <t>TiwariAnkitb</t>
+  </si>
+  <si>
+    <t>Radhey_Radhey_1</t>
+  </si>
+  <si>
+    <t>DexterMatis0489</t>
+  </si>
+  <si>
+    <t>NicholasJackm10</t>
+  </si>
+  <si>
+    <t>Zartaj20031</t>
   </si>
   <si>
     <t>ArshiaZojaji</t>
   </si>
   <si>
+    <t>gornyhor</t>
+  </si>
+  <si>
+    <t>VaibhavSinghDev</t>
+  </si>
+  <si>
+    <t>tanja_codes</t>
+  </si>
+  <si>
+    <t>cjski_web3</t>
+  </si>
+  <si>
+    <t>gossdotinc</t>
+  </si>
+  <si>
+    <t>Talkweb03</t>
+  </si>
+  <si>
+    <t>PandeyAshwini9</t>
+  </si>
+  <si>
+    <t>ichabod_721</t>
+  </si>
+  <si>
+    <t>Bs_Alade</t>
+  </si>
+  <si>
+    <t>outerspacesoph</t>
+  </si>
+  <si>
+    <t>TheRealOkanisis</t>
+  </si>
+  <si>
+    <t>web3Learning2</t>
+  </si>
+  <si>
+    <t>Roq411</t>
+  </si>
+  <si>
+    <t>midesofek</t>
+  </si>
+  <si>
+    <t>Justacanuk81</t>
+  </si>
+  <si>
+    <t>Uchewizzy_31</t>
+  </si>
+  <si>
+    <t>saurabh17999</t>
+  </si>
+  <si>
+    <t>_Ayoola01</t>
+  </si>
+  <si>
+    <t>itorobrown814</t>
+  </si>
+  <si>
+    <t>binary_floyd</t>
+  </si>
+  <si>
+    <t>chinedu_sol</t>
+  </si>
+  <si>
+    <t>MakumbaOscar</t>
+  </si>
+  <si>
     <t>0xCylax</t>
   </si>
   <si>
-    <t>Syvelline</t>
-  </si>
-  <si>
-    <t>yc_crypto</t>
-  </si>
-  <si>
-    <t>cjski_web3</t>
-  </si>
-  <si>
-    <t>web3Learning2</t>
-  </si>
-  <si>
-    <t>Maitrayeedas9</t>
-  </si>
-  <si>
-    <t>a20zCrypto</t>
-  </si>
-  <si>
-    <t>0xLesanders</t>
+    <t>audaciousSneha</t>
+  </si>
+  <si>
+    <t>__MikeDrop__</t>
+  </si>
+  <si>
+    <t>WhiteR4bbitt</t>
+  </si>
+  <si>
+    <t>awesamarth_</t>
+  </si>
+  <si>
+    <t>ankit7241</t>
+  </si>
+  <si>
+    <t>SimonFUTURE2</t>
+  </si>
+  <si>
+    <t>SumrenderS</t>
+  </si>
+  <si>
+    <t>aryc_dev</t>
+  </si>
+  <si>
+    <t>josephomotade0</t>
   </si>
   <si>
     <t>rav3kid</t>
   </si>
   <si>
-    <t>Justacanuk81</t>
+    <t>Alutasam</t>
+  </si>
+  <si>
+    <t>CharanSinghTo18</t>
+  </si>
+  <si>
+    <t>panditdhamdhere</t>
+  </si>
+  <si>
+    <t>naps_thelma</t>
+  </si>
+  <si>
+    <t>devarakonda9908</t>
+  </si>
+  <si>
+    <t>AaroshYadav</t>
+  </si>
+  <si>
+    <t>Sergioconstant_</t>
+  </si>
+  <si>
+    <t>SamuelSojin</t>
+  </si>
+  <si>
+    <t>El_Jardon</t>
+  </si>
+  <si>
+    <t>CuddleofDeath</t>
+  </si>
+  <si>
+    <t>aahiknsv</t>
+  </si>
+  <si>
+    <t>avi0_07</t>
+  </si>
+  <si>
+    <t>IDoNutSeeMoney</t>
+  </si>
+  <si>
+    <t>mahesh_19w</t>
+  </si>
+  <si>
+    <t>0_1inspiration</t>
+  </si>
+  <si>
+    <t>shikkhar_</t>
+  </si>
+  <si>
+    <t>SsekiwalaC</t>
+  </si>
+  <si>
+    <t>MayorPella01</t>
+  </si>
+  <si>
+    <t>de_ddon</t>
+  </si>
+  <si>
+    <t>shobhitexe</t>
+  </si>
+  <si>
+    <t>Dev92rishi</t>
   </si>
   <si>
     <t>Daily Update Tweet: 
-Day 5⃣ of #100daysofcode w/ @LearnWeb3DAO
-JavaScript are fundamentals are finished today, wow that was big. 🥳🔥
-worked on:
-1. Objects
-2. Loops
-3. Functions
-#100DaysofCodeLW3 #javascript https://t.co/qdGzkLVdMr</t>
-  </si>
-  <si>
-    <t>Day 19 of #100DaysOfCode 
-- learned about binary search algorithm 
-- learned about receive &amp;amp; revert functions, function modifiers on AU (w4 - 70%) 
-- 'working of Proof of Stake' on @LearnWeb3DAO 
-- added media queries &amp;amp; products page in shopping app project https://t.co/vfAZf7LqYL</t>
-  </si>
-  <si>
-    <t>Day- 38 of #100DaysOfCode 
-✅Spent reading about Ethereum and Bitcoin in-depth and continued freshman track @LearnWeb3DAO 
-✅Completed lesson 1 of solidity @CryptoZombiesHQ 
-Most productive day of a challenge since I picked it again
-#100daysofcodechallenge #100daysofcoding https://t.co/seWOV7BYgr</t>
-  </si>
-  <si>
-    <t>Planning to start #100daysofcode once again. will document my journey here and @LearnWeb3DAO and @scdevstr discord channels. 
-I will plan my calendar this weekend and starting on monday.
-#100DAYSOFCODELW3</t>
-  </si>
-  <si>
-    <t>Alright champs, here's what we are going to do together as web3 community 😎
-As it was officially announced in @LearnWeb3DAO discord, on 9th of January we are going to start community driven #100DaysOfCode challenge. 
-@haardikkk
-@Haezurath
-@KhanAbbas201
-@LarryCutts6
-👇</t>
+Day 7 of #100daysofcode w/ 
+@LearnWeb3DAO
+1. Solved challenge 2 and 3 from Damn Vulnerable Defi.
+here are my solutions 👇</t>
+  </si>
+  <si>
+    <t>Day 9 of #100DaysOfCode with 
+@LearnWeb3DAO
+-JS iterator practice
+-Cryptozombies review 
+-GitHub update 
+#100DaysofCodeLW3
+#Web3
+#web3community</t>
+  </si>
+  <si>
+    <t>Day 7 of #100daysofcode w/ @LearnWeb3DAO 
+Solidity🚀
+1. CryptoZombies module 1
+#100DaysofCodeLW3 https://t.co/8nMNmf0Lvl</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 7 of #100daysofcode @LearnWeb3DAO
+1. Solved the Implement Stack Using Queues (No. 225) from Leetcode
+2. Chapter 4 of Solidity in CryptoZombies completed
+3. Chapter 2 of Module 2 in FrontEnd Scrimba course completed
+#100DaysofCodeLW3 https://t.co/TtYaCfe3Lh</t>
+  </si>
+  <si>
+    <t>Day 7 of #100DaysOfCode  w/ @LearnWeb3DAO
+-&amp;gt; Continued NextJS - Static side generation, Modular CSS and Image Components. 
+#100DaysOfCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 7 of #100daysofcode w/ 
+@LearnWeb3DAO
+Signed up for a @ETHGlobal hackathon and did research
+1. Learned about what @Filecoin is!
+2. Learned about the use cases it would be great for!
+#100DaysofCodeLW3 https://t.co/bpzY1eFCOO</t>
+  </si>
+  <si>
+    <t>Day  of #100daysofcode w/ @LearnWeb3DAO
+1. Near completion for a landing page with React
+2. practice more component and data reusability with react
+3. Getting how react makes life easy
+#100DaysofCodeLW3 https://t.co/mi4zCgS6E6</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 7 of #100daysofcode w/ 
+@LearnWeb3DAO
+1. Finally graduate from junior from @LearnWeb3DAO 
+complete the graph indexers assignment on polygon network.
+#100DaysofCodeLW3 https://t.co/PJTQXOqOV8</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 7 of #100daysofcode w/ @LearnWeb3DAO
+Getting familiar with grid and flex layouts.
+#100DaysofCodeLW3
+A week already??? Gotta pace up</t>
+  </si>
+  <si>
+    <t>Day 7 of #100daysofcode w/ 
+@LearnWeb3DAO
+ Explored ethereum documentation - different IDE's browser based, Desktop based. 
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 7 of #100DaysOfCode  w/ @LearnWeb3DAO
+1. Working on a browser extension project using some popular apis
+#100DaysOfCodeLW3 #100Devs</t>
+  </si>
+  <si>
+    <t>Day 5 of #100daysofcode w/ @LearnWeb3DAO
+1. Continued with java Script. 
+2. Revised some solidity concepts.
+3. Started working on some contract.
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 7 of #100daysofcode w/ @LearnWeb3DAO
+1. I’ve passed almost passed 9th chapter of Sophomore
+2. I’ve code a lot today(.sol file, js files)
+Good luck everyone♥️
+#100DaysofCodeLW3 https://t.co/nB6dFZPrZz</t>
+  </si>
+  <si>
+    <t>Day 6 of #100DaysOfCode w/ @LearnWeb3DAO 
+🔷 Practice conditional state change with a proper countdown &amp;amp; by resetting a clock and also adding props. 
+🔷 Learned more about ways of conditional rendering.
+🔷 Will review conditionals more before moving forward.
+#100DaysofCodeLW3 https://t.co/2Z1unoXYJB</t>
+  </si>
+  <si>
+    <t>Day 6 of #100DaysOfCode  w/ 
+@LearnWeb3DAO
+1. Props 
+2. useState Hook
+3. React Developer Tools
+#100DaysOfCodeLW3 #reactjs #javascript #Web3 https://t.co/SnnmmYL0C5</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 6 of #100daysofcode w/ @LearnWeb3DAO
+1.solved @LeetCode daily challenge
+2.studied about transactions in database
+3.studied about file module in python.
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 7 of #100daysofcode w/ 
+@LearnWeb3DAO
+-Continued to freecodecamp Js.
+-Learning more on functions, objects and defining function in objects.
+-Hope to finish tutorials next week and start to build actually!
+#100DaysofCodeLW3 https://t.co/TXJNlWHIxl</t>
+  </si>
+  <si>
+    <t>Day 6 of #100daysofcode w/ @LearnWeb3DAO
+1. Learned about the CRUD paradigm.
+2. Learned the basics of MIME types.
+3. Learned various CSS properties related to font and text manipulation.
+#100DaysofCodeLW3 https://t.co/dBazXWM948</t>
+  </si>
+  <si>
+    <t>5th day of #100DaysOfCode w/@LearnWeb3DAO 
+Today  started with bootstrap:
+1. Containers 
+2. Typography
+3. Badges, Alerts, &amp;amp; Button Groups</t>
+  </si>
+  <si>
+    <t>Day 56 of #100DaysOfCode with @PandeyAshwini9 from @LearnWeb3DAO.
+In Progress....
+-Building sovereign user Owned data profile using Ceramic Network....
+-Joint some twitter space and learnt a lot.
+#100DaysofCodeLW3
+#Web3
+#web3jobs</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 6 of #100daysofcode w/ @LearnWeb3DAO
+Today I started #Ethereum Developer Bootcamp by @AlchemyLearn Week 1:
+1.Bootcamp Introduction
+2.The First Primitive
+3. Digital Signature
+#100DaysofCodeLW3 https://t.co/nDWiBoxgiT</t>
+  </si>
+  <si>
+    <t>Day 6 of #100daysofcode w/ @LearnWeb3DAO
+1⃣ Pulled another 16 str8 hours of prep for Ethereum development🙀Speedrun Eth + scaffold.eth today &amp;amp; loads practice w/ hardhat &amp;amp;🧶
+2⃣ Near finished huge document for use cases &amp;amp; 1st blog article
+3⃣ Read &amp;amp; Network👀⏬🥇
+#100DaysofCodeLW3 https://t.co/TqW92wQGAD</t>
+  </si>
+  <si>
+    <t>Day 6 of #100daysofcode w/ 
+@LearnWeb3DAO
+ninety nine of other #100daysofcoding 
+1. Completed 2 Codewars katas 💪
+2. javascript review-freecodecamp 
+3. Progress on website, exploring social media buttons
+4. listened to Devs Do Something pod episode 🎙️
+#100DaysofCodeLW3 https://t.co/XAnmimrxLb</t>
+  </si>
+  <si>
+    <t>Day 6 of #100daysofcode w/
+@LearnWeb3DAO 
+1.Added dynamic functions to add/remove owner or to change policy in the multisig wallet
+2.Roughly studied about the staking reward and vault contracts, will start building these.
+#100DaysofCodeLW3  #100daysofcodechallenge https://t.co/h2IbQ03YyC</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 1⃣3⃣ of #100daysofcode w/ @LearnWeb3DAO
+It's time to learn about #javascript Theories, after playing with fundamentals. This is something that can give enhance my understanding over upcoming stuff. A lot of developers ignore this topic!
+#100DaysofCodeLW3 https://t.co/5gK3jXFBk5</t>
+  </si>
+  <si>
+    <t>Day 6
+Review Chainlink
+#100DaysOfCode  
+@LearnWeb3DAO
+ #100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 6 of #100daysofcode w/ @LearnWeb3DAO
+1. Didn't do much today. 
+2. Just fixed the image hover on the nft card.
+3. Learning more about Flex and Grid.
+Will try to do some more CSS for few days and implement basic JavaScript with it.
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 6 of #100daysofcode w/ @LearnWeb3DAO
+1. created detailed readme for my whitelist dapp
+2. promised myself to write the readmes first from now on
+3. promised myself to finally keep this promise
+3. pushed whitelist dapp to goerli (after sepolia) to get lw3 nft
+#100DaysofCodeLW3 https://t.co/vyPqgPSMHg</t>
+  </si>
+  <si>
+    <t>Day 6 of #100daysofcode w/ @LearnWeb3DAO
+Continuation of work on the Battleship game.
+1. Created function displaying alive ship count on each board 
+2. Created function to change view of the ship on computer board when is sunk
+3. Added mobile media queries
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 5 of #100daysofcode w/ @LearnWeb3DAO
+1. Completed the second module of @scrimba's javascript course. 
+2. Attended the weekly Cairo bootcamp by @stark_con. Learnt about Zk rollups and a lil introduction to Cairo. 
+#100DaysofCodeLW3 https://t.co/EyegRIkTiN</t>
+  </si>
+  <si>
+    <t>Day 6 of #100daysofcode w/ @LearnWeb3DAO
+Learning Nodejs
+1. Divided my project into routes and controller
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 56 of #100DaysOfCode with @TiwariAnkitb from @LearnWeb3DAO.
+In Progress....
+-Building sovereign user Owned data profile using Ceramic Network....
+-Joint some twitter space and learnt a lot.
+#100DaysofCodeLW3
+#Web3
+#web3jobs</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 6 of #100daysofcode w/ @LearnWeb3DAO &amp;amp; @scrimba
+Today's focus
+1. Centering
+2. Padding
+3. Border &amp;amp; border-radius
+#100DaysofCodeLW3 https://t.co/ycVa9Fi1Uw</t>
+  </si>
+  <si>
+    <t>Day 14 of #365DaysOfCode #365DaysOfMe
+Day 5 of #100daysofcode w/ 
+@LearnWeb3DAO #100DaysofCodeLW3
+I'm still on my scrimba react course, I will start the first project tomorrow. I couldn't do a lot today because of church, school work(farm😭) and stress. I meuve tomorrow. https://t.co/Qwvmxrghcf</t>
+  </si>
+  <si>
+    <t>Day 6 of #100daysofcode w/ 
+@LearnWeb3DAO
+1. wrote more scripts for my project 👩‍💻
+2. played capture the ether ⛳️ 
+#100DaysofCodeLW3 https://t.co/bm2HNJsUS1</t>
+  </si>
+  <si>
+    <t>Daily 📰 Tweet:
+Day 6⃣ of #100DaysOfCode &amp;amp; #100DaysOfWeb3 w/ 
+@LearnWeb3DAO
+ ✅ #IPFS gateway running
+ ✅ #Avalanche  node
+ ✅ deployed a site with @fleekxyz  + custom domain + #github!
+#100DaysofCodeLW3
+Day 6 Journal Entry: https://t.co/UY1vSYiLCU</t>
+  </si>
+  <si>
+    <t>@LearnWeb3DAO @DuneAnalytics @CryptoMories Day 6 of #100daysofcode w/ 
+@LearnWeb3DAO
+Not a lot to show today, started the CS50 week 7 #SQL lecture. Want to know everything about SQL before the next steps!
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 5 of #100daysofcode w/ 
+@LearnWeb3DAO 
+1. Still working on Meme Generator project 
+@scrimba, it's a long and interactive one tho! Learning a ton🥳
+9% =&amp;gt; 31% https://t.co/yr0e6xUnJX</t>
+  </si>
+  <si>
+    <t>Day 6 of #100daysofcode w/ @LearnWeb3DAO
+It's weekend, but is it really weekend? Building must continue💪🏽 
+So today, I went harder into the "Ternary ( ? ) operator" and implemented it into different scenarios.
+Check it out😉
+#100DaysofCodeLW3 https://t.co/UUYCrgAyIh</t>
+  </si>
+  <si>
+    <t>Day 6 of @LearnWeb3DAO #100DaysOfCode  , today I completed @unity essentials pathway which included developing a learning plan and goals. On to the Junior developer pathway 🎉 #programming #blockchain #gaming #developer #crypto https://t.co/OmJ36yKePR</t>
+  </si>
+  <si>
+    <t>Day 6 of #100daysofcode w/ @LearnWeb3DAO
+ Worked on styling of the tribute page project.
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 5 of #100daysofcode w/  @LearnWeb3DAO
+No progress today tho:
+✅Started my new portfolio and created some figma designs.
+✅ Learned it hard way about burnouts.
+✅ Learn about few stuff that we don't know existed.
+(Thread incoming)
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 6 of #100daysofcode @LearnWeb3DAO
+1. Rectified the issues with the lite-server, with the  help of a boss @cjski_web3 and continue with the dApp building under @LearnWeb3DAO, presently writing the smart contract  #100DaysofCodeLW3 
+@Haezurath @cjski_web3 https://t.co/Gd4OT29q0R</t>
+  </si>
+  <si>
+    <t>Day [4] of #100daysofcode @LearnWeb3DAO
+Today I  learned more on JavaScript,  and I am happy to say that I was able to solve some beginner problems without needing any help... 
+JavaScript is an important part in my journey to being a blockchain developer.
+#100DaysofCodeLW3 https://t.co/l2iovN0HVZ</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 4 of #100daysofcode w/ @LearnWeb3DAO
+1. Finished the front end of DEX Tutorial
+2. Deployed the app to vercel - https://t.co/HHz7VyUQdH
+3. Graduated Sophomore Level
+#100DaysofCodeLW3 https://t.co/E7YxgM3zKn</t>
+  </si>
+  <si>
+    <t>Day 6 of #100daysofCode w/ @LearnWeb3DAO 
+-Completed the lesson on Re-entrancy Attack
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 4 of #100daysofcode
+ w/ 
+@LearnWeb3DAO
+1) Continued with  the 
+@ethernaut challenges
+2) lesson 5 of @PatrickAlphaC freecodecamp coursework 
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 5 of #100DaysOfCode 
+- Building React project 
+- Learning about ether js 
+- learning redux
+#100DaysofCodeLW3 @LearnWeb3DAO</t>
+  </si>
+  <si>
+    <t>Day 3 and 4 of #100daysofcode w/ @LearnWeb3DAO
+Very hectic 🥲🥴
+1. JavaScript Javascript and JavaScript by @AlchemyLearn
+2. Cairo Bootcamp Session 2 by @stark_con
+3. Worked on the thread left with the final edit.
+4. Started First Freelance Gig of the Year.
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 3 of #100daysofcode w/ 
+@LearnWeb3DAO
+1. Made some more progress in my JS course.
+2. Did more C++
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 3 of #100daysofcode w/ @LearnWeb3DAO
+📦Add a method call from a dependency &amp;amp;&amp;amp; error === true (yay!)
+(2🐦1🥌) Refactored my component into a utility and removed this error.
+📝I have run into something similar and plan to put something out to help with it.
+#100DaysofCodeLW3 https://t.co/mGN6OnL7bo</t>
+  </si>
+  <si>
+    <t>Day 4 of #100DaysOfCode : Yet another practice project using Node and Express. Also started level 12 of @LearnWeb3DAO's Sophomore track: DAO</t>
+  </si>
+  <si>
+    <t>Day 67 of #100DaysOfCode 
+Day 4 of #100DaysofCodeLW3  w @LearnWeb3DAO 
+⏩Made significant progress by continuing to study EVM Opcodes, despite the challenges
+⏩Got selected to Tezos Buildercamp 1.0
+⏩Got into @developer_dao 
+All in all, it was a productive and successful day.</t>
+  </si>
+  <si>
+    <t>I'm joining the #100daysofcode challenge with the 
+@LearnWeb3DAO community! 💻
+Focusing on Web3 development for 100 days!
+Join us here👇
+https://t.co/3DbyDv678l
+#100DaysofCodeLW3 
+Day 3 Completed -  PyTEAL Study, Senior Progression, Encode Homework, Merkle Tree
+$SELF on $Algo</t>
+  </si>
+  <si>
+    <t>Day 3 of #100DaysOfCode with 
+@LearnWeb3DAO
+1. Leetcode daily problem
+2. react, firestore onSnapshot usage
+3. studying Theory of Computation for semester exams.
+If anyone can help me find resources to use onSnapshot with react js, please do tell.
+#100DaysofCodeLW3 #Web3 https://t.co/mMRZGkF8QN</t>
+  </si>
+  <si>
+    <t>Day 3 of #100daysofcode w/ 
+@LearnWeb3DAO
+1. Learnt Bootstrap halfway there. Feeling better today.
+2. Read about some NFT use cases, will follow @LearnWeb3DAO NFT tutorial of freshman track maybe after 3 days. Focusing on CSS currently.
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day3 #100DaysofCodeLW3 #100DaysOfCode 
+I am still on my real estate smart contract, and happy to commit to this. Also having an idea of a music smart contract, what feature would you love to see in the music smart contract.
+ #100daysofcode w/ @LearnWeb3DAO https://t.co/Xh1fX09aT0</t>
+  </si>
+  <si>
+    <t>Day 2 of #100daysofcode w/ @LearnWeb3DAO
+Worked on the Week1 assignment of Alchemy Learn's Ethereum Developer Bootcamp
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 2 of the #100DaysOfCode with @LearnWeb3DAO. went back to my freshman course and almost done
+#100DaysOfCode 
+#100daysofcodechallenge 
+#100DaysofCodeLW3 
+#100daysofcoding https://t.co/gf2V7qHxi9</t>
+  </si>
+  <si>
+    <t>Day 5 of #100daysofcode w/ 
+@LearnWeb3DAO
+Completed a practice part module in js @scrimba 
+Explored ethereum documentation about decentralized storage.
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>I'm gonna joining the #100daysofcode challenge with the my favourite @LearnWeb3DAO community! 
+Want to be web 3 developer ? 
+Upgrade your skills ?
+Join us here👇
+https://t.co/OXxvdQ0rEH
+We all will be focusing on Web3 development for 100 days!
+#100DaysofCodeLW3 LFG 💥</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 1 of #100daysofcode @LearnWeb3DAO
+1. Blockchain user state
+2. Tree Data structures 
+3. Blockchain Data storage 
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Tambien estamos haciendo 
+#100DaysOfCode  w/ @LearnWeb3DAO
+así que si les interesa les voy mostrando mis avances en la plataforma
+como el De-Fi Exchange que creamos en el segundo nivel 💪 https://t.co/Vp6g8DGmDh</t>
+  </si>
+  <si>
+    <t>@LearnWeb3DAO 
+Nice work @NicholasJackm10! 💪 You're making great progress with your #100daysofcode. Keep up the good work! 🔥</t>
+  </si>
+  <si>
+    <t>i will update my 100days thread with @LearnWeb3DAO for the next 100 days  
+Day [1] of #100daysofcode 
+#100DaysOfCode https://t.co/fkVNz3t8HV</t>
+  </si>
+  <si>
+    <t>Day 1 of #100DaysOfCodeLW3 with 1 minute left before it turns into day 2 here (Central US Timezone :D ) 
+What did I do for today's #100DaysOfCode? I brushed up on some Solana dev, did some Rust troubleshooting, and voila, Hello world program deployed!
+@LearnWeb3DAO https://t.co/TsPd87fIls</t>
+  </si>
+  <si>
+    <t>Everyone participating in  #100DaysOfCode .
+You guys are absolutely smashing it !!
+Gonna start it tomorrow!!! 
+Also, I invite you to try @Valist_io for your project deployment (psst... Your projects will be on-chain 👀 )
+@LearnWeb3DAO to the moon and beyond 🚀</t>
+  </si>
+  <si>
+    <t>@awesamarth_ @LearnWeb3DAO Congrats buddy💯🚀
+I am also thinking of starting #100DaysOfCode</t>
+  </si>
+  <si>
+    <t>Day 1 of #100daysofcode w/ @LearnWeb3DAO
+1. Going to work on Python (started awhile back but fell off and haven't done any work in months and never really committed or had any accountability)
+2. Created Github account and forked the 100 days of code log</t>
+  </si>
+  <si>
+    <t>Yayyy! I completed the Intro to Programming lesson on @LearnWeb3DAO with a perfect score! 
+Day 1 of #100daysofcode
+#100daysofdayscodeLW3
+What are you waiting for? Join me in learning web3 at https://t.co/Um2z8sXVn0</t>
+  </si>
+  <si>
+    <t>I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community.
+We'll be focusing on Web3 development for 100 days.
+Join us here:
+https://t.co/uEHyJj3Nva
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Excited to start 100daysofcode with my fav @LearnWeb3DAO ✨✨✨</t>
+  </si>
+  <si>
+    <t>@nithinchandranp @LearnWeb3DAO Wish you all the best in your 100 days of code Nithin.</t>
+  </si>
+  <si>
+    <t>Daily Tweet Update 
+Day (1)of #100DaysOfCode with @LearnWeb3DAO 
+1. It made me started my freshman course
+2. Very knowledgeable and outstanding 
+3. Also got familiar with Javascripts https://t.co/m4ID4O0g3v</t>
   </si>
   <si>
     <t>I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community! 💻
 We'll be focusing on Web3 development for 100 days!
 Join us here👇
-https://t.co/WmBIxayEod
+https://t.co/lGZhecfR3O
 #100DaysofCodeLW3</t>
   </si>
   <si>
-    <t>I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community! 💻
-I’ll be focusing on Web3 development for 100 days!
-Starting from January 9th.</t>
-  </si>
-  <si>
-    <t>Wanted to get an early head start...
-Day 1 of #100DaysOfCode with @LearnWeb3DAO
--Research on effective GitHub use
--JavaScript Rock, Paper, Scissors program focusing on different JS function syntax
-#100DaysofCodeLW3
-#Web3
-#web3community 
-@Codecademy</t>
-  </si>
-  <si>
-    <t>Day 4-5 | #100DaysOfWeb3 &amp;amp; #100DaysOfCode 
-• Finished Solidity Course 
-I will work on my final project for practicum.
-• Also will follow Freshman level on @LearnWeb3DAO https://t.co/A6aYqEjLZn</t>
-  </si>
-  <si>
-    <t>I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community! 💻
-We'll be focusing on Web3 development for 100 days!
-Join us here👇
-https://t.co/SyVMQByYkK
-#100DaysofCodeLW3</t>
-  </si>
-  <si>
-    <t>I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community! 💻
-We'll be focusing on Web3 development for 100 days!
-Join us here👇
-https://t.co/9epZdiLLFL
-#100DaysofCodeLW3</t>
-  </si>
-  <si>
-    <t>https://twitter.com/ArshiaZojaji/status/1611393669428350979</t>
-  </si>
-  <si>
-    <t>https://twitter.com/0xCylax/status/1611394241904926721</t>
-  </si>
-  <si>
-    <t>https://twitter.com/Syvelline/status/1611059503746928640</t>
-  </si>
-  <si>
-    <t>https://twitter.com/yc_crypto/status/1610929639576293376</t>
-  </si>
-  <si>
-    <t>https://twitter.com/cjski_web3/status/1610812225807056896</t>
-  </si>
-  <si>
-    <t>https://twitter.com/web3Learning2/status/1611323420074975232</t>
-  </si>
-  <si>
-    <t>https://twitter.com/Maitrayeedas9/status/1611314578625028096</t>
-  </si>
-  <si>
-    <t>https://twitter.com/a20zCrypto/status/1611478248202047488</t>
-  </si>
-  <si>
-    <t>https://twitter.com/0xLesanders/status/1611705616476831744</t>
-  </si>
-  <si>
-    <t>https://twitter.com/rav3kid/status/1611626477900165123</t>
-  </si>
-  <si>
-    <t>https://twitter.com/Justacanuk81/status/1611756569502552070</t>
+    <t>@Radhey_Radhey_1 @pytwt3 @LearnWeb3DAO Lol, awesome! Keep up the good work! #100daysofcode</t>
+  </si>
+  <si>
+    <t>@awesamarth_ @LearnWeb3DAO Great consistency brother. I am also going to start #100DaysOfCode from tomorrow</t>
+  </si>
+  <si>
+    <t>https://twitter.com/AamirUsmani1552/status/1614640080185970688</t>
+  </si>
+  <si>
+    <t>https://twitter.com/a20zCrypto/status/1614478384922497024</t>
+  </si>
+  <si>
+    <t>https://twitter.com/nandagopan__/status/1614683329974145025</t>
+  </si>
+  <si>
+    <t>https://twitter.com/nithinchandranp/status/1614605118351212549</t>
+  </si>
+  <si>
+    <t>https://twitter.com/2xprathamesh/status/1614684482979889153</t>
+  </si>
+  <si>
+    <t>https://twitter.com/ChaffieRN/status/1614650971295981570</t>
+  </si>
+  <si>
+    <t>https://twitter.com/HanabiPlug/status/1614655804052758528</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Maitrayeedas9/status/1614660584427114496</t>
+  </si>
+  <si>
+    <t>https://twitter.com/dazkool69/status/1614604814272561152</t>
+  </si>
+  <si>
+    <t>https://twitter.com/manoharsspace/status/1614677295146598400</t>
+  </si>
+  <si>
+    <t>https://twitter.com/kushagrasarathe/status/1614649072459321344</t>
+  </si>
+  <si>
+    <t>https://twitter.com/RitikkAgarwalll/status/1614528798254563331</t>
+  </si>
+  <si>
+    <t>https://twitter.com/blagoichelovek/status/1614680499544268800</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Jbusta2103/status/1614444316210122756</t>
+  </si>
+  <si>
+    <t>https://twitter.com/_0x416B68696C_/status/1614477732532084737</t>
+  </si>
+  <si>
+    <t>https://twitter.com/karthik___gk/status/1614642212415111168</t>
+  </si>
+  <si>
+    <t>https://twitter.com/yc_crypto/status/1614620500885372928</t>
+  </si>
+  <si>
+    <t>https://twitter.com/vundnido/status/1614457175773954059</t>
+  </si>
+  <si>
+    <t>https://twitter.com/seamlesslyjj/status/1614118692522004480</t>
+  </si>
+  <si>
+    <t>https://twitter.com/TiwariAnkitb/status/1614306646624440323</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Radhey_Radhey_1/status/1614296269341720577</t>
+  </si>
+  <si>
+    <t>https://twitter.com/DexterMatis0489/status/1614480102628155393</t>
+  </si>
+  <si>
+    <t>https://twitter.com/NicholasJackm10/status/1614337878850666496</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Zartaj20031/status/1614667211808940034</t>
+  </si>
+  <si>
+    <t>https://twitter.com/ArshiaZojaji/status/1614678971832049666</t>
+  </si>
+  <si>
+    <t>https://twitter.com/gornyhor/status/1614526084195794945</t>
+  </si>
+  <si>
+    <t>https://twitter.com/VaibhavSinghDev/status/1614367190693859332</t>
+  </si>
+  <si>
+    <t>https://twitter.com/tanja_codes/status/1614359956030988292</t>
+  </si>
+  <si>
+    <t>https://twitter.com/cjski_web3/status/1614392891249463296</t>
+  </si>
+  <si>
+    <t>https://twitter.com/gossdotinc/status/1614337557713780737</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Talkweb03/status/1614351790626988037</t>
+  </si>
+  <si>
+    <t>https://twitter.com/PandeyAshwini9/status/1614314370712100864</t>
+  </si>
+  <si>
+    <t>https://twitter.com/ichabod_721/status/1614428497379819525</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Bs_Alade/status/1614405461897535488</t>
+  </si>
+  <si>
+    <t>https://twitter.com/outerspacesoph/status/1614442787491164163</t>
+  </si>
+  <si>
+    <t>https://twitter.com/TheRealOkanisis/status/1614414344594554880</t>
+  </si>
+  <si>
+    <t>https://twitter.com/web3Learning2/status/1614646665847128064</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Roq411/status/1614439893916155904</t>
+  </si>
+  <si>
+    <t>https://twitter.com/midesofek/status/1614395213749039104</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Justacanuk81/status/1614314318065029120</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Uchewizzy_31/status/1614399242163863555</t>
+  </si>
+  <si>
+    <t>https://twitter.com/saurabh17999/status/1613938544812388353</t>
+  </si>
+  <si>
+    <t>https://twitter.com/_Ayoola01/status/1614386995597553665</t>
+  </si>
+  <si>
+    <t>https://twitter.com/itorobrown814/status/1613981231343087618</t>
+  </si>
+  <si>
+    <t>https://twitter.com/binary_floyd/status/1614049695550308352</t>
+  </si>
+  <si>
+    <t>https://twitter.com/chinedu_sol/status/1614386211329646593</t>
+  </si>
+  <si>
+    <t>https://twitter.com/MakumbaOscar/status/1613575704519610374</t>
+  </si>
+  <si>
+    <t>https://twitter.com/0xCylax/status/1613592319797907456</t>
+  </si>
+  <si>
+    <t>https://twitter.com/audaciousSneha/status/1614359155908964353</t>
+  </si>
+  <si>
+    <t>https://twitter.com/__MikeDrop__/status/1613630458641670145</t>
+  </si>
+  <si>
+    <t>https://twitter.com/WhiteR4bbitt/status/1614470509030432769</t>
+  </si>
+  <si>
+    <t>https://twitter.com/awesamarth_/status/1614536345137082368</t>
+  </si>
+  <si>
+    <t>https://twitter.com/ankit7241/status/1613599231369154560</t>
+  </si>
+  <si>
+    <t>https://twitter.com/SimonFUTURE2/status/1613408204268130306</t>
+  </si>
+  <si>
+    <t>https://twitter.com/SumrenderS/status/1613239398560321537</t>
+  </si>
+  <si>
+    <t>https://twitter.com/aryc_dev/status/1613597442989252608</t>
+  </si>
+  <si>
+    <t>https://twitter.com/josephomotade0/status/1613796796698099712</t>
+  </si>
+  <si>
+    <t>https://twitter.com/rav3kid/status/1612857411953647617</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Alutasam/status/1612932154542923780</t>
+  </si>
+  <si>
+    <t>https://twitter.com/CharanSinghTo18/status/1613990328331304961</t>
+  </si>
+  <si>
+    <t>https://twitter.com/panditdhamdhere/status/1612497998889779200</t>
+  </si>
+  <si>
+    <t>https://twitter.com/naps_thelma/status/1612573766097293334</t>
+  </si>
+  <si>
+    <t>https://twitter.com/devarakonda9908/status/1613996069632806946</t>
+  </si>
+  <si>
+    <t>https://twitter.com/AaroshYadav/status/1613997783328952330</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Sergioconstant_/status/1614030035559788544</t>
+  </si>
+  <si>
+    <t>https://twitter.com/SamuelSojin/status/1613325565167284225</t>
+  </si>
+  <si>
+    <t>https://twitter.com/El_Jardon/status/1613327638981926912</t>
+  </si>
+  <si>
+    <t>https://twitter.com/CuddleofDeath/status/1612690686393843712</t>
+  </si>
+  <si>
+    <t>https://twitter.com/aahiknsv/status/1612881430153154560</t>
+  </si>
+  <si>
+    <t>https://twitter.com/avi0_07/status/1613446417732747264</t>
+  </si>
+  <si>
+    <t>https://twitter.com/IDoNutSeeMoney/status/1612894504134258689</t>
+  </si>
+  <si>
+    <t>https://twitter.com/mahesh_19w/status/1612845702006341633</t>
+  </si>
+  <si>
+    <t>https://twitter.com/0_1inspiration/status/1612621616374075394</t>
+  </si>
+  <si>
+    <t>https://twitter.com/shikkhar_/status/1612682573511282693</t>
+  </si>
+  <si>
+    <t>https://twitter.com/SsekiwalaC/status/1612292399325118464</t>
+  </si>
+  <si>
+    <t>https://twitter.com/MayorPella01/status/1612765966630256640</t>
+  </si>
+  <si>
+    <t>https://twitter.com/de_ddon/status/1612841506041102337</t>
+  </si>
+  <si>
+    <t>https://twitter.com/shobhitexe/status/1613205884364099585</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Dev92rishi/status/1614581597566820352</t>
   </si>
 </sst>
 </file>
@@ -554,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -579,16 +1447,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>168</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -596,67 +1464,67 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>170</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>33</v>
+        <v>171</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>172</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -664,16 +1532,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>173</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -681,16 +1549,16 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>174</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -698,66 +1566,1222 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E10">
         <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E11">
         <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12">
         <v>7</v>
       </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="C19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
         <v>40</v>
       </c>
-      <c r="E12">
+      <c r="C30" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E31">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E34">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" t="s">
+        <v>124</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" t="s">
+        <v>125</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" t="s">
+        <v>126</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" t="s">
+        <v>128</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" t="s">
+        <v>129</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" t="s">
+        <v>131</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" t="s">
+        <v>133</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" t="s">
+        <v>134</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" t="s">
+        <v>136</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" t="s">
+        <v>137</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E48">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" t="s">
+        <v>138</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E50">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" t="s">
+        <v>140</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" t="s">
+        <v>62</v>
+      </c>
+      <c r="C52" t="s">
+        <v>141</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" t="s">
+        <v>142</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" t="s">
+        <v>143</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" t="s">
+        <v>144</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E55">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" t="s">
+        <v>145</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" t="s">
+        <v>67</v>
+      </c>
+      <c r="C57" t="s">
+        <v>146</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" t="s">
+        <v>147</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" t="s">
+        <v>148</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>10</v>
+      </c>
+      <c r="B60" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60" t="s">
+        <v>149</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" t="s">
+        <v>71</v>
+      </c>
+      <c r="C61" t="s">
+        <v>150</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" t="s">
+        <v>72</v>
+      </c>
+      <c r="C62" t="s">
+        <v>151</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" t="s">
+        <v>152</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64" t="s">
+        <v>150</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" t="s">
+        <v>75</v>
+      </c>
+      <c r="C65" t="s">
+        <v>150</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" t="s">
+        <v>76</v>
+      </c>
+      <c r="C66" t="s">
+        <v>153</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67" t="s">
+        <v>154</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" t="s">
+        <v>78</v>
+      </c>
+      <c r="C68" t="s">
+        <v>155</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>10</v>
+      </c>
+      <c r="B69" t="s">
+        <v>79</v>
+      </c>
+      <c r="C69" t="s">
+        <v>156</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>10</v>
+      </c>
+      <c r="B70" t="s">
+        <v>80</v>
+      </c>
+      <c r="C70" t="s">
+        <v>157</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>8</v>
+      </c>
+      <c r="B71" t="s">
+        <v>81</v>
+      </c>
+      <c r="C71" t="s">
+        <v>158</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>10</v>
+      </c>
+      <c r="B72" t="s">
+        <v>82</v>
+      </c>
+      <c r="C72" t="s">
+        <v>159</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>10</v>
+      </c>
+      <c r="B73" t="s">
+        <v>83</v>
+      </c>
+      <c r="C73" t="s">
+        <v>160</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>10</v>
+      </c>
+      <c r="B74" t="s">
+        <v>84</v>
+      </c>
+      <c r="C74" t="s">
+        <v>161</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>10</v>
+      </c>
+      <c r="B75" t="s">
+        <v>85</v>
+      </c>
+      <c r="C75" t="s">
+        <v>162</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" t="s">
+        <v>86</v>
+      </c>
+      <c r="C76" t="s">
+        <v>163</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>10</v>
+      </c>
+      <c r="B77" t="s">
+        <v>87</v>
+      </c>
+      <c r="C77" t="s">
+        <v>164</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>10</v>
+      </c>
+      <c r="B78" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" t="s">
+        <v>165</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79" t="s">
+        <v>89</v>
+      </c>
+      <c r="C79" t="s">
+        <v>166</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>5</v>
+      </c>
+      <c r="B80" t="s">
+        <v>90</v>
+      </c>
+      <c r="C80" t="s">
+        <v>167</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E80">
         <v>1</v>
       </c>
     </row>
@@ -774,6 +2798,74 @@
     <hyperlink ref="D10" r:id="rId9"/>
     <hyperlink ref="D11" r:id="rId10"/>
     <hyperlink ref="D12" r:id="rId11"/>
+    <hyperlink ref="D13" r:id="rId12"/>
+    <hyperlink ref="D14" r:id="rId13"/>
+    <hyperlink ref="D15" r:id="rId14"/>
+    <hyperlink ref="D16" r:id="rId15"/>
+    <hyperlink ref="D17" r:id="rId16"/>
+    <hyperlink ref="D18" r:id="rId17"/>
+    <hyperlink ref="D19" r:id="rId18"/>
+    <hyperlink ref="D20" r:id="rId19"/>
+    <hyperlink ref="D21" r:id="rId20"/>
+    <hyperlink ref="D22" r:id="rId21"/>
+    <hyperlink ref="D23" r:id="rId22"/>
+    <hyperlink ref="D24" r:id="rId23"/>
+    <hyperlink ref="D25" r:id="rId24"/>
+    <hyperlink ref="D26" r:id="rId25"/>
+    <hyperlink ref="D27" r:id="rId26"/>
+    <hyperlink ref="D28" r:id="rId27"/>
+    <hyperlink ref="D29" r:id="rId28"/>
+    <hyperlink ref="D30" r:id="rId29"/>
+    <hyperlink ref="D31" r:id="rId30"/>
+    <hyperlink ref="D32" r:id="rId31"/>
+    <hyperlink ref="D33" r:id="rId32"/>
+    <hyperlink ref="D34" r:id="rId33"/>
+    <hyperlink ref="D35" r:id="rId34"/>
+    <hyperlink ref="D36" r:id="rId35"/>
+    <hyperlink ref="D37" r:id="rId36"/>
+    <hyperlink ref="D38" r:id="rId37"/>
+    <hyperlink ref="D39" r:id="rId38"/>
+    <hyperlink ref="D40" r:id="rId39"/>
+    <hyperlink ref="D41" r:id="rId40"/>
+    <hyperlink ref="D42" r:id="rId41"/>
+    <hyperlink ref="D43" r:id="rId42"/>
+    <hyperlink ref="D44" r:id="rId43"/>
+    <hyperlink ref="D45" r:id="rId44"/>
+    <hyperlink ref="D46" r:id="rId45"/>
+    <hyperlink ref="D47" r:id="rId46"/>
+    <hyperlink ref="D48" r:id="rId47"/>
+    <hyperlink ref="D49" r:id="rId48"/>
+    <hyperlink ref="D50" r:id="rId49"/>
+    <hyperlink ref="D51" r:id="rId50"/>
+    <hyperlink ref="D52" r:id="rId51"/>
+    <hyperlink ref="D53" r:id="rId52"/>
+    <hyperlink ref="D54" r:id="rId53"/>
+    <hyperlink ref="D55" r:id="rId54"/>
+    <hyperlink ref="D56" r:id="rId55"/>
+    <hyperlink ref="D57" r:id="rId56"/>
+    <hyperlink ref="D58" r:id="rId57"/>
+    <hyperlink ref="D59" r:id="rId58"/>
+    <hyperlink ref="D60" r:id="rId59"/>
+    <hyperlink ref="D61" r:id="rId60"/>
+    <hyperlink ref="D62" r:id="rId61"/>
+    <hyperlink ref="D63" r:id="rId62"/>
+    <hyperlink ref="D64" r:id="rId63"/>
+    <hyperlink ref="D65" r:id="rId64"/>
+    <hyperlink ref="D66" r:id="rId65"/>
+    <hyperlink ref="D67" r:id="rId66"/>
+    <hyperlink ref="D68" r:id="rId67"/>
+    <hyperlink ref="D69" r:id="rId68"/>
+    <hyperlink ref="D70" r:id="rId69"/>
+    <hyperlink ref="D71" r:id="rId70"/>
+    <hyperlink ref="D72" r:id="rId71"/>
+    <hyperlink ref="D73" r:id="rId72"/>
+    <hyperlink ref="D74" r:id="rId73"/>
+    <hyperlink ref="D75" r:id="rId74"/>
+    <hyperlink ref="D76" r:id="rId75"/>
+    <hyperlink ref="D77" r:id="rId76"/>
+    <hyperlink ref="D78" r:id="rId77"/>
+    <hyperlink ref="D79" r:id="rId78"/>
+    <hyperlink ref="D80" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/lw3Tweets.xlsx
+++ b/lw3Tweets.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="453">
   <si>
     <t>Date Created</t>
   </si>
@@ -31,562 +31,1023 @@
     <t>DaysOfCoding</t>
   </si>
   <si>
+    <t>(2023, 2, 20)</t>
+  </si>
+  <si>
+    <t>(2023, 2, 18)</t>
+  </si>
+  <si>
+    <t>(2023, 2, 19)</t>
+  </si>
+  <si>
+    <t>(2023, 2, 14)</t>
+  </si>
+  <si>
+    <t>(2023, 2, 10)</t>
+  </si>
+  <si>
+    <t>(2023, 2, 9)</t>
+  </si>
+  <si>
+    <t>(2023, 2, 7)</t>
+  </si>
+  <si>
+    <t>(2023, 2, 6)</t>
+  </si>
+  <si>
+    <t>(2023, 2, 11)</t>
+  </si>
+  <si>
+    <t>(2023, 2, 4)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 31)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 27)</t>
+  </si>
+  <si>
+    <t>(2023, 2, 1)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 25)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 29)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 19)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 22)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 18)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 17)</t>
+  </si>
+  <si>
+    <t>(2023, 2, 8)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 21)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 13)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 12)</t>
+  </si>
+  <si>
+    <t>(2023, 2, 3)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 14)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 11)</t>
+  </si>
+  <si>
+    <t>(2023, 2, 2)</t>
+  </si>
+  <si>
+    <t>(2023, 2, 12)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 30)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 23)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 26)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 10)</t>
+  </si>
+  <si>
+    <t>(2023, 1, 24)</t>
+  </si>
+  <si>
     <t>(2023, 1, 15)</t>
   </si>
   <si>
-    <t>(2023, 1, 14)</t>
-  </si>
-  <si>
-    <t>(2023, 1, 13)</t>
-  </si>
-  <si>
-    <t>(2023, 1, 12)</t>
-  </si>
-  <si>
-    <t>(2023, 1, 11)</t>
-  </si>
-  <si>
-    <t>(2023, 1, 10)</t>
-  </si>
-  <si>
     <t>(2023, 1, 9)</t>
   </si>
   <si>
+    <t>ChaffieRN</t>
+  </si>
+  <si>
+    <t>dazkool69</t>
+  </si>
+  <si>
+    <t>HanabiPlug</t>
+  </si>
+  <si>
+    <t>nithinchandranp</t>
+  </si>
+  <si>
+    <t>a20zCrypto</t>
+  </si>
+  <si>
+    <t>tanja_codes</t>
+  </si>
+  <si>
+    <t>gossdotinc</t>
+  </si>
+  <si>
+    <t>karthik___gk</t>
+  </si>
+  <si>
+    <t>cjski_web3</t>
+  </si>
+  <si>
     <t>AamirUsmani1552</t>
   </si>
   <si>
-    <t>a20zCrypto</t>
+    <t>TheRealOkanisis</t>
+  </si>
+  <si>
+    <t>Jbusta2103</t>
+  </si>
+  <si>
+    <t>Zartaj20031</t>
+  </si>
+  <si>
+    <t>outerspacesoph</t>
+  </si>
+  <si>
+    <t>RitikkAgarwalll</t>
+  </si>
+  <si>
+    <t>ankit7241</t>
+  </si>
+  <si>
+    <t>NicholasJackm10</t>
+  </si>
+  <si>
+    <t>yc_crypto</t>
+  </si>
+  <si>
+    <t>Uchewizzy_31</t>
+  </si>
+  <si>
+    <t>_Ayoola01</t>
+  </si>
+  <si>
+    <t>2xprathamesh</t>
+  </si>
+  <si>
+    <t>manoharsspace</t>
+  </si>
+  <si>
+    <t>Gayathri1903</t>
   </si>
   <si>
     <t>nandagopan__</t>
   </si>
   <si>
-    <t>nithinchandranp</t>
-  </si>
-  <si>
-    <t>2xprathamesh</t>
-  </si>
-  <si>
-    <t>ChaffieRN</t>
-  </si>
-  <si>
-    <t>HanabiPlug</t>
+    <t>PandeyAshwini9</t>
+  </si>
+  <si>
+    <t>TiwariAnkitb</t>
+  </si>
+  <si>
+    <t>Kazim_walid</t>
+  </si>
+  <si>
+    <t>midesofek</t>
+  </si>
+  <si>
+    <t>Talkweb03</t>
+  </si>
+  <si>
+    <t>kushagrasarathe</t>
+  </si>
+  <si>
+    <t>Mr_MicDaniel</t>
+  </si>
+  <si>
+    <t>vundnido</t>
+  </si>
+  <si>
+    <t>naps_thelma</t>
+  </si>
+  <si>
+    <t>aryc_dev</t>
+  </si>
+  <si>
+    <t>Bs_Alade</t>
+  </si>
+  <si>
+    <t>gornyhor</t>
+  </si>
+  <si>
+    <t>DexterMatis0489</t>
+  </si>
+  <si>
+    <t>itorobrown814</t>
+  </si>
+  <si>
+    <t>stormyymrots</t>
+  </si>
+  <si>
+    <t>Ketan_14n</t>
+  </si>
+  <si>
+    <t>VaibhavSinghDev</t>
+  </si>
+  <si>
+    <t>blagoichelovek</t>
+  </si>
+  <si>
+    <t>web3Learning2</t>
+  </si>
+  <si>
+    <t>chinedu_sol</t>
+  </si>
+  <si>
+    <t>ActivateGlacier</t>
+  </si>
+  <si>
+    <t>Harshpatil03</t>
+  </si>
+  <si>
+    <t>Radhey_Radhey_1</t>
+  </si>
+  <si>
+    <t>iamanilmhj</t>
+  </si>
+  <si>
+    <t>WhiteR4bbitt</t>
+  </si>
+  <si>
+    <t>panditdhamdhere</t>
+  </si>
+  <si>
+    <t>0xSan3</t>
+  </si>
+  <si>
+    <t>Justacanuk81</t>
+  </si>
+  <si>
+    <t>_0x416B68696C_</t>
+  </si>
+  <si>
+    <t>3aglefly</t>
+  </si>
+  <si>
+    <t>ShivamBarke</t>
+  </si>
+  <si>
+    <t>binary_floyd</t>
+  </si>
+  <si>
+    <t>rav3kid</t>
   </si>
   <si>
     <t>Maitrayeedas9</t>
   </si>
   <si>
-    <t>dazkool69</t>
-  </si>
-  <si>
-    <t>manoharsspace</t>
-  </si>
-  <si>
-    <t>kushagrasarathe</t>
-  </si>
-  <si>
-    <t>RitikkAgarwalll</t>
-  </si>
-  <si>
-    <t>blagoichelovek</t>
-  </si>
-  <si>
-    <t>Jbusta2103</t>
-  </si>
-  <si>
-    <t>_0x416B68696C_</t>
-  </si>
-  <si>
-    <t>karthik___gk</t>
-  </si>
-  <si>
-    <t>yc_crypto</t>
-  </si>
-  <si>
-    <t>vundnido</t>
-  </si>
-  <si>
     <t>seamlesslyjj</t>
   </si>
   <si>
-    <t>TiwariAnkitb</t>
-  </si>
-  <si>
-    <t>Radhey_Radhey_1</t>
-  </si>
-  <si>
-    <t>DexterMatis0489</t>
-  </si>
-  <si>
-    <t>NicholasJackm10</t>
-  </si>
-  <si>
-    <t>Zartaj20031</t>
+    <t>SimonFUTURE2</t>
+  </si>
+  <si>
+    <t>ShivDixit21</t>
   </si>
   <si>
     <t>ArshiaZojaji</t>
   </si>
   <si>
-    <t>gornyhor</t>
-  </si>
-  <si>
-    <t>VaibhavSinghDev</t>
-  </si>
-  <si>
-    <t>tanja_codes</t>
-  </si>
-  <si>
-    <t>cjski_web3</t>
-  </si>
-  <si>
-    <t>gossdotinc</t>
-  </si>
-  <si>
-    <t>Talkweb03</t>
-  </si>
-  <si>
-    <t>PandeyAshwini9</t>
+    <t>ThirdMistrust</t>
   </si>
   <si>
     <t>ichabod_721</t>
   </si>
   <si>
-    <t>Bs_Alade</t>
-  </si>
-  <si>
-    <t>outerspacesoph</t>
-  </si>
-  <si>
-    <t>TheRealOkanisis</t>
-  </si>
-  <si>
-    <t>web3Learning2</t>
-  </si>
-  <si>
     <t>Roq411</t>
   </si>
   <si>
-    <t>midesofek</t>
-  </si>
-  <si>
-    <t>Justacanuk81</t>
-  </si>
-  <si>
-    <t>Uchewizzy_31</t>
+    <t>singh_vaibhav08</t>
+  </si>
+  <si>
+    <t>pushprotocol</t>
+  </si>
+  <si>
+    <t>awesamarth_</t>
   </si>
   <si>
     <t>saurabh17999</t>
   </si>
   <si>
-    <t>_Ayoola01</t>
-  </si>
-  <si>
-    <t>itorobrown814</t>
-  </si>
-  <si>
-    <t>binary_floyd</t>
-  </si>
-  <si>
-    <t>chinedu_sol</t>
-  </si>
-  <si>
     <t>MakumbaOscar</t>
   </si>
   <si>
-    <t>0xCylax</t>
+    <t>MarkusEicher70</t>
+  </si>
+  <si>
+    <t>__MikeDrop__</t>
+  </si>
+  <si>
+    <t>NyambegaBray</t>
+  </si>
+  <si>
+    <t>0xChinedu</t>
+  </si>
+  <si>
+    <t>sawxnhere</t>
+  </si>
+  <si>
+    <t>josephomotade0</t>
   </si>
   <si>
     <t>audaciousSneha</t>
   </si>
   <si>
-    <t>__MikeDrop__</t>
-  </si>
-  <si>
-    <t>WhiteR4bbitt</t>
-  </si>
-  <si>
-    <t>awesamarth_</t>
-  </si>
-  <si>
-    <t>ankit7241</t>
-  </si>
-  <si>
-    <t>SimonFUTURE2</t>
+    <t>Ayodeji7111</t>
+  </si>
+  <si>
+    <t>Vaibhavs_twt</t>
+  </si>
+  <si>
+    <t>JackD_eth</t>
+  </si>
+  <si>
+    <t>naitik_shrma</t>
   </si>
   <si>
     <t>SumrenderS</t>
   </si>
   <si>
-    <t>aryc_dev</t>
-  </si>
-  <si>
-    <t>josephomotade0</t>
-  </si>
-  <si>
-    <t>rav3kid</t>
+    <t>sriram_s_s</t>
+  </si>
+  <si>
+    <t>Saurabhh_Web3</t>
+  </si>
+  <si>
+    <t>Agrim_Sharma174</t>
+  </si>
+  <si>
+    <t>CryptoAxiom</t>
+  </si>
+  <si>
+    <t>lite_745</t>
+  </si>
+  <si>
+    <t>Robertsteacher1</t>
+  </si>
+  <si>
+    <t>rahul3526</t>
+  </si>
+  <si>
+    <t>Ch8992</t>
+  </si>
+  <si>
+    <t>temple_snowden</t>
+  </si>
+  <si>
+    <t>muqtadirsandha</t>
+  </si>
+  <si>
+    <t>jadernalia</t>
+  </si>
+  <si>
+    <t>RobertLeeSaund</t>
+  </si>
+  <si>
+    <t>CharanSinghTo18</t>
+  </si>
+  <si>
+    <t>LarryCutts6</t>
+  </si>
+  <si>
+    <t>samueloh99</t>
+  </si>
+  <si>
+    <t>mokhteeb74</t>
+  </si>
+  <si>
+    <t>tajamul9342</t>
+  </si>
+  <si>
+    <t>topagentmike007</t>
+  </si>
+  <si>
+    <t>wilbermayflore1</t>
+  </si>
+  <si>
+    <t>thehapadev</t>
+  </si>
+  <si>
+    <t>DrMelvaMitchel1</t>
+  </si>
+  <si>
+    <t>NG8world</t>
+  </si>
+  <si>
+    <t>avi0_07</t>
+  </si>
+  <si>
+    <t>Web3_Manu</t>
+  </si>
+  <si>
+    <t>mahesh_19w</t>
+  </si>
+  <si>
+    <t>ShivamJ0502</t>
+  </si>
+  <si>
+    <t>greg_aloi</t>
+  </si>
+  <si>
+    <t>0x0DeeDee</t>
+  </si>
+  <si>
+    <t>AaroshYadav</t>
+  </si>
+  <si>
+    <t>YashSolanki_</t>
+  </si>
+  <si>
+    <t>devarakonda9908</t>
+  </si>
+  <si>
+    <t>0_1inspiration</t>
+  </si>
+  <si>
+    <t>SamuelSojin</t>
+  </si>
+  <si>
+    <t>02b2YBH</t>
+  </si>
+  <si>
+    <t>WiliBastar</t>
+  </si>
+  <si>
+    <t>Sergioconstant_</t>
+  </si>
+  <si>
+    <t>imkunaal02</t>
+  </si>
+  <si>
+    <t>CuddleofDeath</t>
+  </si>
+  <si>
+    <t>MayorPella01</t>
   </si>
   <si>
     <t>Alutasam</t>
   </si>
   <si>
-    <t>CharanSinghTo18</t>
-  </si>
-  <si>
-    <t>panditdhamdhere</t>
-  </si>
-  <si>
-    <t>naps_thelma</t>
-  </si>
-  <si>
-    <t>devarakonda9908</t>
-  </si>
-  <si>
-    <t>AaroshYadav</t>
-  </si>
-  <si>
-    <t>Sergioconstant_</t>
-  </si>
-  <si>
-    <t>SamuelSojin</t>
+    <t>cryptowithabhi</t>
+  </si>
+  <si>
+    <t>LoogtanP</t>
+  </si>
+  <si>
+    <t>Varunx10</t>
+  </si>
+  <si>
+    <t>aahiknsv</t>
+  </si>
+  <si>
+    <t>Dev92rishi</t>
+  </si>
+  <si>
+    <t>bj8697</t>
+  </si>
+  <si>
+    <t>Vaibhavs_8</t>
+  </si>
+  <si>
+    <t>saikrishna2023</t>
+  </si>
+  <si>
+    <t>shikkhar_</t>
+  </si>
+  <si>
+    <t>de_ddon</t>
+  </si>
+  <si>
+    <t>Mind56045188</t>
+  </si>
+  <si>
+    <t>KhanAbbas201</t>
   </si>
   <si>
     <t>El_Jardon</t>
   </si>
   <si>
-    <t>CuddleofDeath</t>
-  </si>
-  <si>
-    <t>aahiknsv</t>
-  </si>
-  <si>
-    <t>avi0_07</t>
+    <t>SsekiwalaC</t>
   </si>
   <si>
     <t>IDoNutSeeMoney</t>
   </si>
   <si>
-    <t>mahesh_19w</t>
-  </si>
-  <si>
-    <t>0_1inspiration</t>
-  </si>
-  <si>
-    <t>shikkhar_</t>
-  </si>
-  <si>
-    <t>SsekiwalaC</t>
-  </si>
-  <si>
-    <t>MayorPella01</t>
-  </si>
-  <si>
-    <t>de_ddon</t>
-  </si>
-  <si>
-    <t>shobhitexe</t>
-  </si>
-  <si>
-    <t>Dev92rishi</t>
+    <t>rohitscode</t>
+  </si>
+  <si>
+    <t>Vaibhavtwts</t>
+  </si>
+  <si>
+    <t>Day 43 of #100daysofcode w/ @LearnWeb3DAO
+Learned how you can actually read private variable values from any smart contract
+1. Learned what private stands for
+2. Learned how to read this value from storage
+Building in public, follow to stay up-to-date🙌#100DaysofCodeLW https://t.co/H7ae1G40VT</t>
   </si>
   <si>
     <t>Daily Update Tweet: 
-Day 7 of #100daysofcode w/ 
+Day 42 of #100daysofcode w/ @LearnWeb3DAO
+Completed cryptozombies lesson no 1
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 43 of #100daysofcode w/ @LearnWeb3DAO
+1. did a foundation reading on DOM relationship with javascript
+2. played around with an existing program game to work it
+#100DaysofCodeLW3 https://t.co/utpCJCDCvI</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 43 of #100daysofcode @LearnWeb3DAO
+1. Solved the problem Remove Duplicates From Sorted Array(No. 26) from Leetcode
+2. Completed the chapter 6 Build a Chrome Extension on Scrimba(100%)
+#100DaysofCodeLW3 https://t.co/Eh2RmHKjul</t>
+  </si>
+  <si>
+    <t>Day 45 of #100DaysOfCode with 
 @LearnWeb3DAO
-1. Solved challenge 2 and 3 from Damn Vulnerable Defi.
-here are my solutions 👇</t>
-  </si>
-  <si>
-    <t>Day 9 of #100DaysOfCode with 
+-@JavaScript on @AlchemyLearn
+-data structures 
+-GitHub updates 
+#GitGud
+#100DaysofCodeLW3
+#Web3</t>
+  </si>
+  <si>
+    <t>Day 43 of #100daysofcode w/ @LearnWeb3DAO
+1.  built a simple Task Tracking app on Flow for LW3's course
+2. finished my first Flow Quest
+3. attended a tokenomics intro workshop organized by Flow
+#100DaysofCodeLW3 https://t.co/zdMOBLKRjp</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 42 of #100daysofcode w/ @LearnWeb3DAO
+Resumed the sophomore track from lw3 that had been set aside for quite some time. 
+Learnt about React hooks - useState and useEffect. 
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 42 of #100daysofcode w/ @LearnWeb3DAO
+1.solved @LeetCode daily challenge
+2. read about tkinter module in python
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 43 of #100daysofcode w/ @LearnWeb3DAO
+Working on CryptoCave shop. 
+1. Implemented add to basked function
+2. Added checkout details component
+3. Custom themes
+Now I am working on changing quantity of the items and should be ready to ship it tomorrow 🤗
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 39 of #100daysofcode w/ 
 @LearnWeb3DAO
--JS iterator practice
--Cryptozombies review 
--GitHub update 
-#100DaysofCodeLW3
+College is messing up everything. Nothing done today. 
+Since I have broken the streak, I am quitting the Challenge. Not getting time to work on web3 security or anything.
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Daily 📰
+Day 4️⃣2⃣/1⃣0⃣0⃣
+ ✅ merkle hash trees with @LearnWeb3DAO  
+ ✅ @developer_dao mentee prep for the AM!
+#100DaysofCodeLW3 #100DaysOfCode #100DaysOfWeb3 @LearnWeb3DAO
+📔 https://t.co/jAGyay1hun https://t.co/T6b8cDE4GQ</t>
+  </si>
+  <si>
+    <t>Day 41 of #100DaysOfCode w/ @LearnWeb3DAO
+🔷 Started the meme generator
+🔷 finished the OOP course from @freeCodeCamp 
+🔷 Continued reviewing ES6 features 
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 40 of #100daysofcode w/
+@LearnWeb3DAO
+Studied details of storage gas consumption and refund of gas. Did experiments on it by deploying various contracts and interacting with them.
+Worked on the hackathon project.
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 41 of #100daysofcode w/ 
+@LearnWeb3DAO
+-started coding a task tracker dApp ✅
+-played crypto zombies 🧟‍♀️
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 40 of #100DaysOfCode  w/ 
+@LearnWeb3DAO  
+1. Completed one project.
+2. Started working on other project.
+3. Doing some Java collage stuff.
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 105 of #100daysofcoding  
+Day 42 of #100DaysOfCode  w/ 
+@LearnWeb3DAO
+ ⏩ Continued working on the project
+⏩ Played around with arcana network
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 43 of #100daysofcode w/ 
+@LearnWeb3DAO
+played around with Git Branching website
+worked on codewars kata
+#100DaysofCodeLW3 https://t.co/ii1ivCYoGl</t>
+  </si>
+  <si>
+    <t>Day 36 of  #100daysofcode w/ 
+@LearnWeb3DAO
+-I have completed a one of the certification project on freecodecamp.
+-It is called telephone number validator.
+-It returns true or false based on the provided string is structured as phone number or not.
+#100DaysofCodeLW3 https://t.co/Lk61djyDB7</t>
+  </si>
+  <si>
+    <t>Day 43 of #100daysofcode w/ 
+@LearnWeb3DAO 
+Study on c programming.
+Completed chapter 4,
+starting some programming projects on it next.
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 43  of #100daysofcode 
+@LearnWeb3DAO
+Completed my first  NFT Collection under the sophomore course 
+@LearnWeb3DAO
+@Haezurath
+@cjski_web3
+@LarryCutts6 https://t.co/oatt7Pec1m</t>
+  </si>
+  <si>
+    <t>Day 32-35 of #100DaysOfCode  w/ 
+@LearnWeb3DAO
+Worked on ReactJs + tailwind + three.js websites.
+Continued Frontend Career Path @scrimba 
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 33 of #100daysofcode w/ 
+@LearnWeb3DAO
+Working on ethforall project 
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 3⃣1⃣ of #100DaysOfCode w/@LearnWeb3DAO 
+Learning about providers, signers and ABIs
+#100DaysofCodeLW3 https://t.co/7o9LyRJxM6</t>
+  </si>
+  <si>
+    <t>Day 30 of #100daysofcode w/ @LearnWeb3DAO
+1. created a simple NFT marketplace on @0xPolygon using @thirdweb framework
+2. @scrimba- Learn React / Project_02
+#100DaysofCodeLW3 https://t.co/xoXUHqWlOQ</t>
+  </si>
+  <si>
+    <t>@TiwariAnkitb Day 81 of #100DaysOfCode with @TiwariAnkitb from @LearnWeb3DAO.
+In Security (60%✅)...
+ - Detect legit-looking contracts which are actually malicious (1-2 hours)..........
 #Web3
 #web3community</t>
   </si>
   <si>
-    <t>Day 7 of #100daysofcode w/ @LearnWeb3DAO 
-Solidity🚀
-1. CryptoZombies module 1
-#100DaysofCodeLW3 https://t.co/8nMNmf0Lvl</t>
-  </si>
-  <si>
-    <t>Daily Update Tweet: 
-Day 7 of #100daysofcode @LearnWeb3DAO
-1. Solved the Implement Stack Using Queues (No. 225) from Leetcode
-2. Chapter 4 of Solidity in CryptoZombies completed
-3. Chapter 2 of Module 2 in FrontEnd Scrimba course completed
-#100DaysofCodeLW3 https://t.co/TtYaCfe3Lh</t>
-  </si>
-  <si>
-    <t>Day 7 of #100DaysOfCode  w/ @LearnWeb3DAO
--&amp;gt; Continued NextJS - Static side generation, Modular CSS and Image Components. 
-#100DaysOfCodeLW3</t>
-  </si>
-  <si>
-    <t>Day 7 of #100daysofcode w/ 
+    <t>Day 81 of #100DaysOfCode with @PandeyAshwini9 from @LearnWeb3DAO.
+In Security (60%✅)...
+ - Detect legit-looking contracts which are actually malicious (1-2 hours)..........
+#Web3
+#web3community</t>
+  </si>
+  <si>
+    <t>Day 29 of #100daysofcode w/ 
 @LearnWeb3DAO
-Signed up for a @ETHGlobal hackathon and did research
-1. Learned about what @Filecoin is!
-2. Learned about the use cases it would be great for!
-#100DaysofCodeLW3 https://t.co/bpzY1eFCOO</t>
-  </si>
-  <si>
-    <t>Day  of #100daysofcode w/ @LearnWeb3DAO
-1. Near completion for a landing page with React
-2. practice more component and data reusability with react
-3. Getting how react makes life easy
-#100DaysofCodeLW3 https://t.co/mi4zCgS6E6</t>
-  </si>
-  <si>
-    <t>Daily Update Tweet: 
-Day 7 of #100daysofcode w/ 
+1- finished 1 challenge on Damn vulnerable defi.
+2- doing research on ERC1967proxy and ERC1967upgrade and proxy contract and understand how their functionality works. 
+I'm following @cmichelio Auditing roadmap blog.
+#100DaysOfCode</t>
+  </si>
+  <si>
+    <t>Day 32 of #100daysofcode w/ 
 @LearnWeb3DAO
-1. Finally graduate from junior from @LearnWeb3DAO 
-complete the graph indexers assignment on polygon network.
-#100DaysofCodeLW3 https://t.co/PJTQXOqOV8</t>
-  </si>
-  <si>
-    <t>Daily Update Tweet: 
-Day 7 of #100daysofcode w/ @LearnWeb3DAO
-Getting familiar with grid and flex layouts.
+1. Built the frontend side for a NFT Minting dApp for NinjaDash (Image in the comments)
+2. Wrote a BlogPost on Hashnode ✍🏼
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 33 of #100daysofcode w/ 
+@LearnWeb3DAO
+- updated some c# endpoints
+- created smart contract using concordium
+- created a repo in dockerhub
+- pushed my dockerized app to the repo.
+- deployed it on K8s 
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 30 - 32 of #100DaysOfCode  w/ @LearnWeb3DAO
+Day 30 - Learnt to use useLoader in react
+Day 31 - Solved 2 typescript problems on codewars
+Day 32 - Building a minesweeper game in react today
+#100DaysOfCodeLW3 #100Devs</t>
+  </si>
+  <si>
+    <t>1
+Day 28 of #100daysofcode w/ 
+@LearnWeb3DAO
+Day 17:  #30daysweb3security w/ 
+@Web3SecurityDAO
+Today, I worked on the Ethernault Recovery challenge and began my React Frontend Class through @scrimba 
+Link to my project - https://t.co/4xIrUT5ydO
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 26 of #100daysofcode w/ @LearnWeb3DAO
+1. Learned about payable functions in solidity.
+2. Reviewed how to send Ether with send, transfer, and call. 
+3.  Studied receive() and fallback() functions.
+4. Played around with some code. 
+#100DaysofCodeLW3 https://t.co/wAbRHp2CTH</t>
+  </si>
+  <si>
+    <t>Day 36 of #100daysofcode w/ 
+@LearnWeb3DAO 
+Practiced more on scope and JavaScript compiler.
+Got my environment ready for this week @encodeclub bootcamp lesson.
+ #100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 22 of #100daysofcode w/ 
+@LearnWeb3DAO
+1. Continuing with DOM learning, almost done
+2.Bit of Java today
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 35 of #365DaysOfCode
+Day 26 of #100daysofcode w/ 
+@LearnWeb3DAO
 #100DaysofCodeLW3
-A week already??? Gotta pace up</t>
-  </si>
-  <si>
-    <t>Day 7 of #100daysofcode w/ 
-@LearnWeb3DAO
- Explored ethereum documentation - different IDE's browser based, Desktop based. 
-#100DaysofCodeLW3</t>
-  </si>
-  <si>
-    <t>Day 7 of #100DaysOfCode  w/ @LearnWeb3DAO
-1. Working on a browser extension project using some popular apis
-#100DaysOfCodeLW3 #100Devs</t>
-  </si>
-  <si>
-    <t>Day 5 of #100daysofcode w/ @LearnWeb3DAO
-1. Continued with java Script. 
-2. Revised some solidity concepts.
-3. Started working on some contract.
-#100DaysofCodeLW3</t>
-  </si>
-  <si>
-    <t>Daily Update Tweet: 
-Day 7 of #100daysofcode w/ @LearnWeb3DAO
-1. I’ve passed almost passed 9th chapter of Sophomore
-2. I’ve code a lot today(.sol file, js files)
-Good luck everyone♥️
-#100DaysofCodeLW3 https://t.co/nB6dFZPrZz</t>
-  </si>
-  <si>
-    <t>Day 6 of #100DaysOfCode w/ @LearnWeb3DAO 
-🔷 Practice conditional state change with a proper countdown &amp;amp; by resetting a clock and also adding props. 
-🔷 Learned more about ways of conditional rendering.
-🔷 Will review conditionals more before moving forward.
-#100DaysofCodeLW3 https://t.co/2Z1unoXYJB</t>
-  </si>
-  <si>
-    <t>Day 6 of #100DaysOfCode  w/ 
-@LearnWeb3DAO
-1. Props 
-2. useState Hook
-3. React Developer Tools
-#100DaysOfCodeLW3 #reactjs #javascript #Web3 https://t.co/SnnmmYL0C5</t>
-  </si>
-  <si>
-    <t>Daily Update Tweet: 
-Day 6 of #100daysofcode w/ @LearnWeb3DAO
-1.solved @LeetCode daily challenge
-2.studied about transactions in database
-3.studied about file module in python.
-#100DaysofCodeLW3</t>
-  </si>
-  <si>
-    <t>Daily Update Tweet: 
-Day 7 of #100daysofcode w/ 
-@LearnWeb3DAO
--Continued to freecodecamp Js.
--Learning more on functions, objects and defining function in objects.
--Hope to finish tutorials next week and start to build actually!
-#100DaysofCodeLW3 https://t.co/TXJNlWHIxl</t>
-  </si>
-  <si>
-    <t>Day 6 of #100daysofcode w/ @LearnWeb3DAO
-1. Learned about the CRUD paradigm.
-2. Learned the basics of MIME types.
-3. Learned various CSS properties related to font and text manipulation.
-#100DaysofCodeLW3 https://t.co/dBazXWM948</t>
-  </si>
-  <si>
-    <t>5th day of #100DaysOfCode w/@LearnWeb3DAO 
-Today  started with bootstrap:
-1. Containers 
-2. Typography
-3. Badges, Alerts, &amp;amp; Button Groups</t>
-  </si>
-  <si>
-    <t>Day 56 of #100DaysOfCode with @PandeyAshwini9 from @LearnWeb3DAO.
-In Progress....
--Building sovereign user Owned data profile using Ceramic Network....
--Joint some twitter space and learnt a lot.
-#100DaysofCodeLW3
-#Web3
-#web3jobs</t>
-  </si>
-  <si>
-    <t>Daily Update Tweet: 
-Day 6 of #100daysofcode w/ @LearnWeb3DAO
-Today I started #Ethereum Developer Bootcamp by @AlchemyLearn Week 1:
-1.Bootcamp Introduction
-2.The First Primitive
-3. Digital Signature
-#100DaysofCodeLW3 https://t.co/nDWiBoxgiT</t>
-  </si>
-  <si>
-    <t>Day 6 of #100daysofcode w/ @LearnWeb3DAO
-1⃣ Pulled another 16 str8 hours of prep for Ethereum development🙀Speedrun Eth + scaffold.eth today &amp;amp; loads practice w/ hardhat &amp;amp;🧶
-2⃣ Near finished huge document for use cases &amp;amp; 1st blog article
-3⃣ Read &amp;amp; Network👀⏬🥇
-#100DaysofCodeLW3 https://t.co/TqW92wQGAD</t>
-  </si>
-  <si>
-    <t>Day 6 of #100daysofcode w/ 
-@LearnWeb3DAO
-ninety nine of other #100daysofcoding 
-1. Completed 2 Codewars katas 💪
-2. javascript review-freecodecamp 
-3. Progress on website, exploring social media buttons
-4. listened to Devs Do Something pod episode 🎙️
-#100DaysofCodeLW3 https://t.co/XAnmimrxLb</t>
-  </si>
-  <si>
-    <t>Day 6 of #100daysofcode w/
-@LearnWeb3DAO 
-1.Added dynamic functions to add/remove owner or to change policy in the multisig wallet
-2.Roughly studied about the staking reward and vault contracts, will start building these.
-#100DaysofCodeLW3  #100daysofcodechallenge https://t.co/h2IbQ03YyC</t>
-  </si>
-  <si>
-    <t>Daily Update Tweet: 
-Day 1⃣3⃣ of #100daysofcode w/ @LearnWeb3DAO
-It's time to learn about #javascript Theories, after playing with fundamentals. This is something that can give enhance my understanding over upcoming stuff. A lot of developers ignore this topic!
-#100DaysofCodeLW3 https://t.co/5gK3jXFBk5</t>
-  </si>
-  <si>
-    <t>Day 6
-Review Chainlink
-#100DaysOfCode  
+So today was mostly about setting up(for local coding). I installed yarn, solc, FS-extra, ganache and ethers. I just encountered a minor bug but I can’t fix it yet so I’m researching. I meuve https://t.co/D4Iey6NPA6</t>
+  </si>
+  <si>
+    <t>Day 24
+Verify smart contract code on Etherscan
+#100DaysOfCode 
 @LearnWeb3DAO
  #100DaysofCodeLW3</t>
   </si>
   <si>
+    <t>Day 25 of #100daysofcode w/ 
+@LearnWeb3DAO
+1⃣ Reading🎶
+~Quadratic sharding😆
+~AVAX uses subnets of validators
+~Solona Proof of History
+ ~FLOW separates the jobs of validator node into four different roles &amp;amp; allows for upgradable smart contracts using Cadence🔰
+ #100DaysofCodeLW3 https://t.co/Hn50GmOWZH</t>
+  </si>
+  <si>
+    <t>Day [21]of #100daysofcode  
+@LearnWeb3DAO
+Today, I learned about Immediately Invoked Function Expressions.
+The syntax goes like this:
+(function(name){
+console.log("Hello " + name) 
+})( "Twitter")
+Output: Hello Twitter.
+The function is covered in parentheses
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 23 of #100daysofcode w/ 
+@LearnWeb3DAO
+Studied data structures with more emphasis on stack and queue and also did some project work 
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 22 of #100DaysOfCode w/ @LearnWeb3DAO
+1. Completed 1st module (Introduction to Blockchain) of @0xblocktrain "Complete DEFI Course".
+#100Devs #100DaysofCodeLW3</t>
+  </si>
+  <si>
     <t>Daily Update Tweet: 
-Day 6 of #100daysofcode w/ @LearnWeb3DAO
-1. Didn't do much today. 
-2. Just fixed the image hover on the nft card.
-3. Learning more about Flex and Grid.
-Will try to do some more CSS for few days and implement basic JavaScript with it.
+Day 22 of #100daysofcode w/ @LearnWeb3DAO
+-&gt; Learnt about how the JavaScript code gets executed. The working of JavaScript.
+Learning more about it.
 #100DaysofCodeLW3</t>
   </si>
   <si>
-    <t>Day 6 of #100daysofcode w/ @LearnWeb3DAO
-1. created detailed readme for my whitelist dapp
-2. promised myself to write the readmes first from now on
-3. promised myself to finally keep this promise
-3. pushed whitelist dapp to goerli (after sepolia) to get lw3 nft
-#100DaysofCodeLW3 https://t.co/vyPqgPSMHg</t>
-  </si>
-  <si>
-    <t>Day 6 of #100daysofcode w/ @LearnWeb3DAO
-Continuation of work on the Battleship game.
-1. Created function displaying alive ship count on each board 
-2. Created function to change view of the ship on computer board when is sunk
-3. Added mobile media queries
+    <t>Daily Update Tweet: 
+Day 22 of #100daysofcode w/ @LearnWeb3DAO
+1. https://t.co/PyLgB6dBIz
+2. Done first steps in building of DAO
+Good luck everyone🤍🥶
 #100DaysofCodeLW3</t>
   </si>
   <si>
+    <t>@LearnWeb3DAO @DuneAnalytics @CryptoMories @hildobby_ @EarnWeb3DAO @TheRealOkanisis @agaperste @blur_io Day 33 of #100daysofcode w/ 
+@LearnWeb3DAO
+Continued with my Scrimba Javascript course! Feeling like I am starting to get the hang of it, and slowly fall in love with JS. Doing very simple projects so far, maybe I'll step it up soon!
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Days 23 of #100DaysOfCode w/@LearnWeb3DAO 
+✅ Completed the Ethereum Yellow Paper Course by @AckeeBlockchain 
+✅Read this audit findings checklist here: https://t.co/UI7xsjH68U
+✅Read some audit reports
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 36/100 Log - #100DaysOfCode 
+Goal: Open Edition by Kevin Abosch Dashboard [@flipsidecrypto ]
+Progress:
+- Signed up
+-  🧠about ETH and NFT data 
+- Made mint query
+- Made draft dashboard
+And more... https://t.co/ySHRfqYruN
+#100DaysofCodeLW3 
+@LearnWeb3DAO</t>
+  </si>
+  <si>
+    <t>Day 17 of #100DaysOfCode with @LearnWeb3DAO 
+- Continue working on a clone project
+- Learning so many new and interesting things like NextAuth, useSession Hook, and many more...
+#100DaysofCodeLW3 #buildinpublic https://t.co/gKTt2ROPiL</t>
+  </si>
+  <si>
     <t>Daily Update Tweet: 
-Day 5 of #100daysofcode w/ @LearnWeb3DAO
-1. Completed the second module of @scrimba's javascript course. 
-2. Attended the weekly Cairo bootcamp by @stark_con. Learnt about Zk rollups and a lil introduction to Cairo. 
-#100DaysofCodeLW3 https://t.co/EyegRIkTiN</t>
-  </si>
-  <si>
-    <t>Day 6 of #100daysofcode w/ @LearnWeb3DAO
-Learning Nodejs
-1. Divided my project into routes and controller
+Day 18 of #100daysofcode w/ @LearnWeb3DAO
+Today I build my first dApps and it's amazing day today.
+#100DaysofCodeLW3 https://t.co/VJ6jbnsq4e</t>
+  </si>
+  <si>
+    <t>Day 38 of #100daysofcode w/ @LearnWeb3DAO
+1. completed a daily challenge problem '35. Search Insert Position' on @LeetCode
+2. get started 'Enabling Payments with Circle' campaign in @StackUpHQ 
+#100DaysofCodeLW3  #leetcode</t>
+  </si>
+  <si>
+    <t>Day 15 of #100DaysofCode
+ w/ @LearnWeb3DAO
+⏳Been trying to rest my back.. Long week... 🛌⌚
+🏹Playing around with my ComposeDB App when I can.
+💿Now using local storage vs writing (mostly useless) files
+🔃Load locally saved composites
+🏡Sync to "Local" Node
+#100DaysofCodeLW3 https://t.co/vby8iCfbL0</t>
+  </si>
+  <si>
+    <t>Day 40 ✅ of #100DaysOfCode w/ @LearnWeb3DAO 
+Working on portfolio. 
+Build a Navbar now have to play with more react hooks &amp;amp; tailwind classes! 
+This is how my contribution graph looks like. Show me yours ?
+#100DaysofCodeLW3 https://t.co/w1hVg2uj2r</t>
+  </si>
+  <si>
+    <t>Day 15 of #100DaysOfCode  
+Building React project, cleaned by setup ✌🏻
+#100DaysofCodeLW3 @LearnWeb3DAO https://t.co/EP6FGX3G1H</t>
+  </si>
+  <si>
+    <t>Day 23 of @LearnWeb3DAO #100DaysOfCode , working on @unity junior programmer pathway , today I learned how to create a 3d object from an imported picture then wrap it in @BlenderStudio_ 🎉 will finish Manana 🛌
+#programming #Web3 #webdev #gamedev</t>
+  </si>
+  <si>
+    <t>Day 21 of #100DaysOfCode w/
+@LearnWeb3DAO
+1. Accessibility ReactJS
+2. Went through the Docs on Code-Splitting
+#100DaysofCodeLW3 #React</t>
+  </si>
+  <si>
+    <t>I’ll be putting my #100DaysOfCode w/ @LearnWeb3DAO on a hold for now until after exams. Lots of workload to cover and a limited time. 
+I’ll be back ⏳</t>
+  </si>
+  <si>
+    <t>Day 13 of #100daysofcode w/ @LearnWeb3DAO
+Just solved 15 problems on @codechef ! Pushing myself to increase my logical thinking speed. 💪 
+#coding #CodeChef
 #100DaysofCodeLW3</t>
   </si>
   <si>
-    <t>Day 56 of #100DaysOfCode with @TiwariAnkitb from @LearnWeb3DAO.
-In Progress....
--Building sovereign user Owned data profile using Ceramic Network....
--Joint some twitter space and learnt a lot.
-#100DaysofCodeLW3
-#Web3
-#web3jobs</t>
+    <t>Daily Update Tweet:
+Day 11 of #100daysofcode w/ @LearnWeb3DAO
+- Junior Track
+✅ Completed Lesson #8: Building NFT Collection using @IPFS 
+✅ Completed Lesson #9: Building sovereign user-owned data profiles using @ceramicnetwork 
+#100DaysofCodeLW3 https://t.co/wW4B36DJKL</t>
+  </si>
+  <si>
+    <t>Day 11 of #100daysofcode w/ 
+@LearnWeb3DAO
+Completed 80% of Week 3 in 
+@AlchemyLearn
+ Ethereum Bootcamp.
+Learned and used ethers.js to transfer funds. Learned about providers and signers. 
+#100DaysofCodeLW3</t>
   </si>
   <si>
     <t>Daily Update Tweet: 
-Day 6 of #100daysofcode w/ @LearnWeb3DAO &amp;amp; @scrimba
-Today's focus
-1. Centering
-2. Padding
-3. Border &amp;amp; border-radius
-#100DaysofCodeLW3 https://t.co/ycVa9Fi1Uw</t>
-  </si>
-  <si>
-    <t>Day 14 of #365DaysOfCode #365DaysOfMe
-Day 5 of #100daysofcode w/ 
-@LearnWeb3DAO #100DaysofCodeLW3
-I'm still on my scrimba react course, I will start the first project tomorrow. I couldn't do a lot today because of church, school work(farm😭) and stress. I meuve tomorrow. https://t.co/Qwvmxrghcf</t>
-  </si>
-  <si>
-    <t>Day 6 of #100daysofcode w/ 
+Day 10 of #100daysofcode w/ 
 @LearnWeb3DAO
-1. wrote more scripts for my project 👩‍💻
-2. played capture the ether ⛳️ 
-#100DaysofCodeLW3 https://t.co/bm2HNJsUS1</t>
-  </si>
-  <si>
-    <t>Daily 📰 Tweet:
-Day 6⃣ of #100DaysOfCode &amp;amp; #100DaysOfWeb3 w/ 
+1. it was a long lesson i took after a long time, 
+but finally deployed smart contract on fvm at hyperspace network,
+ready for @ETHGlobal FVM sapce wrap hackathon,
+#100DaysofCodeLW3 https://t.co/Ni5Jb0JKWl</t>
+  </si>
+  <si>
+    <t>day 10 of #100DaysOfCode w/@LearnWeb3DAO following along with videos creating web pages using HTML &amp; CSS.</t>
+  </si>
+  <si>
+    <t>I'm joining the #100daysofcode challenge with the 
 @LearnWeb3DAO
- ✅ #IPFS gateway running
- ✅ #Avalanche  node
- ✅ deployed a site with @fleekxyz  + custom domain + #github!
-#100DaysofCodeLW3
-Day 6 Journal Entry: https://t.co/UY1vSYiLCU</t>
-  </si>
-  <si>
-    <t>@LearnWeb3DAO @DuneAnalytics @CryptoMories Day 6 of #100daysofcode w/ 
+ community! 
+Focusing on Web3 development for 100 days!
+Join us here👇
+https://t.co/3DbyDv678l
+#100DaysofCodeLW3 
+Day 12 - worked on my first #Ebook for #Web3Learning and #Web3MCT MeetUp! 
+Join the conversation!</t>
+  </si>
+  <si>
+    <t>Day 10 of #100DaysOfCode w/ @LearnWeb3DAO 
+-solved 3 leetcode questions taking some help from the discuss colum
+-resumed Doing React and learnt Props and event Handlers
+-Did solidity learnt about mapping</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 1⃣6⃣ of #100daysofcode w/ @LearnWeb3DAO
+Today, my main focus was to practice #this keyword to understand how it works.. Trust me, this is a confusing topic when you want to put it into action.
+#100DaysofCodeLW3 https://t.co/Iaqi3eE1X0</t>
+  </si>
+  <si>
+    <t>Day {26} of #100daysofcode w/ 
 @LearnWeb3DAO
-Not a lot to show today, started the CS50 week 7 #SQL lecture. Want to know everything about SQL before the next steps!
+[Fluctus exercise]
+➡️ Live demo:  https://t.co/3QZZqkNBGC
+➡️Github : https://t.co/y80MEpJqRl
+1. Connect API 
+#100DAYSOFCODELW3
+#Web3 https://t.co/xjsCvpeSGC</t>
+  </si>
+  <si>
+    <t>Day 7 of #100daysofcode w/ @LearnWeb3DAO &amp; @scrimba
+Continuing to work on CSS
+1. Taking 2 days off from coding is not recommended
+2. Don't forget to include style in your border property
+3. Tons of style elements in the simplest designs
+#100DaysofCodeLW3 https://t.co/tctHIK3qj7</t>
+  </si>
+  <si>
+    <t>Day 8 of #100daysofcode w/ 
+@LearnWeb3DAO
+1. Still progressing on the Meme Generator project and learning the useState hook concept and conditional rendering.
+ %48 =&gt; %59
+2. Watched the newest content of @BundlrNetwork 
+SDK for NodeJs.
+https://t.co/niWedGzWfO</t>
+  </si>
+  <si>
+    <t>Daily Update Tweet: 
+Day 30 of #100daysofcode w/ @LearnWeb3DAO
+-&amp;gt; Completed the UI of the JS challenge by Frontend Mentor.
+-&amp;gt; Also, will not be following the challenge for this week due to some reasons. Will start again next Monday✌🏻
 #100DaysofCodeLW3</t>
   </si>
   <si>
-    <t>Day 5 of #100daysofcode w/ 
-@LearnWeb3DAO 
-1. Still working on Meme Generator project 
-@scrimba, it's a long and interactive one tho! Learning a ton🥳
-9% =&amp;gt; 31% https://t.co/yr0e6xUnJX</t>
-  </si>
-  <si>
-    <t>Day 6 of #100daysofcode w/ @LearnWeb3DAO
-It's weekend, but is it really weekend? Building must continue💪🏽 
-So today, I went harder into the "Ternary ( ? ) operator" and implemented it into different scenarios.
-Check it out😉
-#100DaysofCodeLW3 https://t.co/UUYCrgAyIh</t>
-  </si>
-  <si>
-    <t>Day 6 of @LearnWeb3DAO #100DaysOfCode  , today I completed @unity essentials pathway which included developing a learning plan and goals. On to the Junior developer pathway 🎉 #programming #blockchain #gaming #developer #crypto https://t.co/OmJ36yKePR</t>
-  </si>
-  <si>
-    <t>Day 6 of #100daysofcode w/ @LearnWeb3DAO
- Worked on styling of the tribute page project.
-#100DaysofCodeLW3</t>
+    <t>After an incredible week of building, we’re happy to announce the winner of our #100DaysofCode Push challenge with @LearnWeb3DAO 🎉
+Congratulations to Manu @topagentmike007 for his awesome project, Soul Chat💬
+To ALL builders who participated, thank you🙏
+🧵 (1/3)</t>
+  </si>
+  <si>
+    <t>Day 10 of #100DaysOfCode : Finished level 12 and 13 of @LearnWeb3DAO's sophomore track! Gonna be doing a little bit of practice + other stuff before moving on to the  final level</t>
   </si>
   <si>
     <t>Daily Update Tweet: 
@@ -599,45 +1060,45 @@
 #100DaysofCodeLW3</t>
   </si>
   <si>
+    <t>How did you approach the coin flip @ethernaut challenge..
+#web3community #Learnweb3DAO #100DAYSOFCODE</t>
+  </si>
+  <si>
+    <t>Day 5 of #100DaysOfCode w/ @LearnWeb3DAO, @scrimba and @freeCodeCamp
+Lesson 7 of the freshman track in progress ▶️
+First steps with #Solidity on a local #Ganache dev #blockchain. A nice thing, not needing real ETH. A steep learning curve, but pretty cool. ✅
+GNight, folks! 💤 https://t.co/dUrZjEPWLi</t>
+  </si>
+  <si>
     <t>Daily Update Tweet: 
-Day 6 of #100daysofcode @LearnWeb3DAO
-1. Rectified the issues with the lite-server, with the  help of a boss @cjski_web3 and continue with the dApp building under @LearnWeb3DAO, presently writing the smart contract  #100DaysofCodeLW3 
-@Haezurath @cjski_web3 https://t.co/Gd4OT29q0R</t>
-  </si>
-  <si>
-    <t>Day [4] of #100daysofcode @LearnWeb3DAO
-Today I  learned more on JavaScript,  and I am happy to say that I was able to solve some beginner problems without needing any help... 
-JavaScript is an important part in my journey to being a blockchain developer.
-#100DaysofCodeLW3 https://t.co/l2iovN0HVZ</t>
-  </si>
-  <si>
-    <t>Daily Update Tweet: 
-Day 4 of #100daysofcode w/ @LearnWeb3DAO
-1. Finished the front end of DEX Tutorial
-2. Deployed the app to vercel - https://t.co/HHz7VyUQdH
-3. Graduated Sophomore Level
-#100DaysofCodeLW3 https://t.co/E7YxgM3zKn</t>
-  </si>
-  <si>
-    <t>Day 6 of #100daysofCode w/ @LearnWeb3DAO 
--Completed the lesson on Re-entrancy Attack
+Day 3 of #100daysofcode w/ 
+@LearnWeb3DAO
+1. Made some more progress in my JS course.
+2. Did more C++
 #100DaysofCodeLW3</t>
   </si>
   <si>
-    <t>Day 4 of #100daysofcode
- w/ 
+    <t>Day 5 of #100DaysOfCode w/
+@LearnWeb3DAO 
+I just completed #CryptoZombies Lesson 1 and learned the basics of coding a game on #Ethereum. 
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 26 of #100DaysOfCode w/ @LearnWeb3DAO 
+✅Completed the Ethernaut 'Telephone' challenge
+✅Completed the Solidity 101 on Secureum
+✅Refreshed my knowledge on phishing with tx.origin
+#100DaysOfCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 3 of #100daysofcode w/ 
 @LearnWeb3DAO
-1) Continued with  the 
-@ethernaut challenges
-2) lesson 5 of @PatrickAlphaC freecodecamp coursework 
-#100DaysofCodeLW3</t>
-  </si>
-  <si>
-    <t>Day 5 of #100DaysOfCode 
-- Building React project 
-- Learning about ether js 
-- learning redux
-#100DaysofCodeLW3 @LearnWeb3DAO</t>
+I wasn't be able to do much today but still I connected backend with frontend of my side project.
+#100DaysofCodeLW3 #LearnInPublic</t>
+  </si>
+  <si>
+    <t>Day 4 of my #100daysofcoding still working on my real estate smart contract but took the chance to write my music smart contract and also wrote an e-commerce smart contract.
+#100daysofcode w/ @LearnWeb3DAO https://t.co/h8KesKrT5t</t>
   </si>
   <si>
     <t>Day 3 and 4 of #100daysofcode w/ @LearnWeb3DAO
@@ -649,40 +1110,32 @@
 #100DaysofCodeLW3</t>
   </si>
   <si>
+    <t>Starting the new week full of energy 😎🤓
+#tech #web3community @LearnWeb3DAO #100daysOfCode https://t.co/0BKNUmoWJO</t>
+  </si>
+  <si>
     <t>Daily Update Tweet: 
-Day 3 of #100daysofcode w/ 
+Day 23 of #100daysofcode w/ @LearnWeb3DAO
+-&gt; Learnt about hoisting in JavaScript.
+-&gt;Continuing with #javascript30 
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 3 of #100daysofcode w/ 
 @LearnWeb3DAO
-1. Made some more progress in my JS course.
-2. Did more C++
-#100DaysofCodeLW3</t>
-  </si>
-  <si>
-    <t>Day 3 of #100daysofcode w/ @LearnWeb3DAO
-📦Add a method call from a dependency &amp;amp;&amp;amp; error === true (yay!)
-(2🐦1🥌) Refactored my component into a utility and removed this error.
-📝I have run into something similar and plan to put something out to help with it.
-#100DaysofCodeLW3 https://t.co/mGN6OnL7bo</t>
-  </si>
-  <si>
-    <t>Day 4 of #100DaysOfCode : Yet another practice project using Node and Express. Also started level 12 of @LearnWeb3DAO's Sophomore track: DAO</t>
-  </si>
-  <si>
-    <t>Day 67 of #100DaysOfCode 
-Day 4 of #100DaysofCodeLW3  w @LearnWeb3DAO 
-⏩Made significant progress by continuing to study EVM Opcodes, despite the challenges
-⏩Got selected to Tezos Buildercamp 1.0
-⏩Got into @developer_dao 
-All in all, it was a productive and successful day.</t>
-  </si>
-  <si>
-    <t>I'm joining the #100daysofcode challenge with the 
-@LearnWeb3DAO community! 💻
-Focusing on Web3 development for 100 days!
-Join us here👇
-https://t.co/3DbyDv678l
+Re-learned solidity and ether.js
+- Off-chain random number learning is not a safe random number
+- Random game generation</t>
+  </si>
+  <si>
+    <t>getting back on the streak
+forgot to post the daily update tweet so here is
+Day 3-8 of #100daysofcode w/ 
+@LearnWeb3DAO
 #100DaysofCodeLW3 
-Day 3 Completed -  PyTEAL Study, Senior Progression, Encode Homework, Merkle Tree
-$SELF on $Algo</t>
+#100DaysOfCode 
+Completed my HTML CSS project - First webpage
+what I learned 🧵⬇️ https://t.co/i0jCXav0lQ</t>
   </si>
   <si>
     <t>Day 3 of #100DaysOfCode with 
@@ -694,21 +1147,218 @@
 #100DaysofCodeLW3 #Web3 https://t.co/mMRZGkF8QN</t>
   </si>
   <si>
-    <t>Day 3 of #100daysofcode w/ 
+    <t>Day56 of #100DaysOFCode: 
+- Working on the EthForAll hack project
+- also completing @LearnWeb3DAO  sophomore track one by one</t>
+  </si>
+  <si>
+    <t>#Day4 of #100DaysOfCode . Made a Basic Passenger Counter Website using HTML,CSS,JAVASCRIPT.
+Completed another challenge @LearnWeb3DAO . Close to complete the Freshman Course. The References in the challenges are really Helpful.
+GreatWork ! @Haezurath 
+@scrimba 
+#blockchain</t>
+  </si>
+  <si>
+    <t>Day 3 of #100daysofcode w/ @LearnWeb3DAO
+🏹 One question on leetcode 
+🏹 Working on project 
+🏹 Learning more about DEX
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Today I deployed my first smart contract and created my first simple #dApp! 
+It's exciting to see how I can alter the blockchain's state 🛠️ 
+#100DaysOfCode @LearnWeb3DAO made it happen! https://t.co/f8XT8iL7Qp</t>
+  </si>
+  <si>
+    <t>I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community! 💻
+We'll be focusing on Web3 development for 100 days!
+For each day I will complete the following  :
+=&amp;gt;  5  Leetcode problems
+=&amp;gt;  1  hour Web3 content
+Looking forward to making this year amazing</t>
+  </si>
+  <si>
+    <t>Robert Lee Saunders Teacher Day 20 of #100daysofcode @LearnWeb3DAO
+Completed the fallout and coinflip challenges on  ethernaut.Studying more about smart contracts hacks and vulnerabilities
+#programming #coding #Python #Java #javascript #code #coder #CodeNewbie #KnowProgram #java https://t.co/u6bra9sfeA</t>
+  </si>
+  <si>
+    <t>Round 2 .
+Day 30-31 of #100DaysOfCode . @LearnWeb3DAO .
+✅Working on the smooth integration of forms.
+✅ Continued working on exploring wagmi much more.
+✅My github knowledge also improving thanks to @kushagrasarathe article.👇</t>
+  </si>
+  <si>
+    <t>https://t.co/Pl6j7NLNh4
+#100DaysOfCode #CodeNewbie #webDeveloper #frontEnd
+Day 41- #100daysofcode Challenge
+20/2/2023🔮every day one step🚶🏻‍♀️☺️
+Creating an Animated Sliding Menu Indicator with Html CSS &amp;amp; Javascript in two ways
+@LearnWeb3DAO #100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>Day 10 of #100DaysOfCode w/
+@LearnWeb3DAO 
+Learnt about sass(syntactically awesome style sheets) a powerful css pre processor which can be used to create Custom Css libraries 
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>#118 Weekly Push Updates
+What was the last week's theme? Bounties should be pushed.
+Wave 5 Pool x Push @Superfluid HQ Please submit by February 2nd.
+#100DaysofCode x Push @LearnWeb3Dao Submit by February 3rd
+@EthIndiaco #ETHForAll x Push Submissions begin February 4th. https://t.co/FSQGCKaCtp</t>
+  </si>
+  <si>
+    <t>@Gayathri1903 @LearnWeb3DAO How hard would you say the freshman path was? And if you don't mind telling me, did you have any coding experience before those 100daysofcode challenges?</t>
+  </si>
+  <si>
+    <t>Robert Saunders teacher qld Day 27 of #100DaysOfCode  w/ 
 @LearnWeb3DAO
-1. Learnt Bootstrap halfway there. Feeling better today.
-2. Read about some NFT use cases, will follow @LearnWeb3DAO NFT tutorial of freshman track maybe after 3 days. Focusing on CSS currently.
+Working on Clipboard App clone 
+#100DaysofCodeLW3 #programming #coding #Python #Java #javascript #code #coder #100DaysOfCode #CodeNewbie #KnowProgram #javascript #FrontEndDevelopment #FrontEnd #DEVCommunity https://t.co/lkvqvm7n8Z</t>
+  </si>
+  <si>
+    <t>Day 5 of #100daysofcode w/ 
+@LearnWeb3DAO
+Completed a practice part module in js @scrimba 
+Explored ethereum documentation about decentralized storage.
 #100DaysofCodeLW3</t>
   </si>
   <si>
-    <t>Day3 #100DaysofCodeLW3 #100DaysOfCode 
-I am still on my real estate smart contract, and happy to commit to this. Also having an idea of a music smart contract, what feature would you love to see in the music smart contract.
- #100daysofcode w/ @LearnWeb3DAO https://t.co/Xh1fX09aT0</t>
-  </si>
-  <si>
-    <t>Day 2 of #100daysofcode w/ @LearnWeb3DAO
-Worked on the Week1 assignment of Alchemy Learn's Ethereum Developer Bootcamp
+    <t>RIP The 100DaysOfCode Python Twitter Bot I made with the help of @web3Learning2 and @cjski_web3 . Unless there's still some free tier for the twitter api...it might be finished. Cause......$150/month is absurd. THATS ONLY THE FIRST LEVEL 😭 @LearnWeb3DAO https://t.co/xubbRhkxfS</t>
+  </si>
+  <si>
+    <t>Day 4 #100DaysOfCode .
+Today I'll be focusing on @LearnWeb3DAO. Still on the fundamentals hope i can finish the "Freshman" course (basics of web3) today.
+- Blockchain
+- Ethereum
+- Crypto Wallet
+- Solidity
+- dApps
+- Smart Contract
+and of course a little a bit of @letsgetrusty.</t>
+  </si>
+  <si>
+    <t>Day4,5,6 in:#100DaysOfCode for javaScript.
+i built a simple SLIDER by html,css and vanilla javaScript , it was hard but you have to get it.
+how's it ?!
+#100Devs
+#web3community
+@LearnWeb3DAO https://t.co/fOwP66kquh</t>
+  </si>
+  <si>
+    <t>I am attending How to power your web3 dapp using Push workshop | #100daysofCode Challenge w/ LearnWeb3DAO on Luma. Join me! https://t.co/dPPlnmLP2j via @LumaHQ</t>
+  </si>
+  <si>
+    <t>Soul Chat ( new project I built ): https://t.co/C2hb8EDqSK
+Thanks to @LearnWeb3DAO for their courses which helped a lot.
+Notifications done with the help of @pushprotocol 
+1/2 
+#learnweb3 #100DaysOfCode #PoweredbyPush</t>
+  </si>
+  <si>
+    <t>Day 23 of #100daysofcode w/ 
+@LearnWeb3DAO
+explored ethereum documentation -nodes and clients
 #100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>urql graphql'ing 😆 #100daysofcode
+@LearnWeb3DAO @CeloOrg @graphprotocol https://t.co/0A3HdLMDVh</t>
+  </si>
+  <si>
+    <t>Melva Mitchell Day 80 of #100DaysOfCode with 
+from @LearnWeb3DAO
+In Security (60%✅)...
+- Why not to use tx.origin to determine the sender of a transaction (1-2 hours)✅
+#Web3 #programmingwithmosh #deved #webdevelopement #webdesign #programming #coding #Python #Java #javascript https://t.co/fBR2vER9vj</t>
+  </si>
+  <si>
+    <t>@Zartaj20031 @LearnWeb3DAO This 100DaysOfCode is inspiring. I may try it. (apart from work where I write code, I can slip 1H a day for this)</t>
+  </si>
+  <si>
+    <t>@awesamarth_ @LearnWeb3DAO Congrats buddy💯🚀
+I am also thinking of starting #100DaysOfCode</t>
+  </si>
+  <si>
+    <t>Just submitted my hackathon project⚒️
+Enabled PUSH Notifs for DAO members reg. creation, voting, &amp; execution of a proposal
+Seems nothing unusual?🙄
+You felt it right,
+but
+learning🧐PUSH protocol from scratch was INVALUABLE💪
+#100DaysofCode #PoweredbyPush
+@LearnWeb3DAO
+🧵</t>
+  </si>
+  <si>
+    <t>Yayyy! I completed the Intro to Programming lesson on @LearnWeb3DAO with a perfect score! 
+Day 1 of #100daysofcode
+#100daysofdayscodeLW3
+What are you waiting for? Join me in learning web3 at https://t.co/Um2z8sXVn0</t>
+  </si>
+  <si>
+    <t>@sriram_s_s @LearnWeb3DAO Jis hisaab se tu 100 days of code kr rha hai marte dum tak complete nhi kar paayega tu</t>
+  </si>
+  <si>
+    <t>Greg Aloi Singapore Day 71 of #100DaysOfCode from @LearnWeb3DAO
+In Senior track....
+-  Learn how to create Merkle Trees for large airdrops (1-2 hours)✅
+-Trying to contribute to open source in Etherium/Solidity.
+#100DaysofCodeLW3 
+#Web3 
+#web3community 
+#blockchain https://t.co/FmIUAUjuPo</t>
+  </si>
+  <si>
+    <t>Started my web3 journey with Push and Learnweb3DAo, and created Push -Tracker that notify you every day about PUSH price.
+#100DaysofCode #PoweredbyPush https://t.co/L7Ta5u7cPG</t>
+  </si>
+  <si>
+    <t>@cjski_web3 @LearnWeb3DAO I have a feeling you're gonna land a job before the #100DaysOfCode finishes. 
+Keep the consistency 🤘
+You're making great progress 🚀</t>
+  </si>
+  <si>
+    <t>I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community.
+We'll be focusing on Web3 development for 100 days.
+Join us here:
+https://t.co/uEHyJj3Nva
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>@LearnWeb3DAO 
+Nice work @NicholasJackm10! 💪 You're making great progress with your #100daysofcode. Keep up the good work! 🔥</t>
+  </si>
+  <si>
+    <t>@LearnWeb3DAO , @AlchemyLearn , cryptozombies,  cybrary online Web penetration testing, @PatrickAlphaC 16 and 32  hour courses, capture the ether, ethereum speed run, ethernaut ..all COMPLETED..so....what's next #code #cybersecuritytips #UK #100DaysOfCode #GreatBritain #developer</t>
+  </si>
+  <si>
+    <t>Tambien estamos haciendo 
+#100DaysOfCode  w/ @LearnWeb3DAO
+así que si les interesa les voy mostrando mis avances en la plataforma
+como el De-Fi Exchange que creamos en el segundo nivel 💪 https://t.co/Vp6g8DGmDh</t>
+  </si>
+  <si>
+    <t>Hey Buidlers!! 👋🏻
+Join #100DaysOfCode  by @LearnWeb3DAO with @pushprotocol 👨‍💻&lt;/&gt;
+Join live workshop starting from today 9:30-10:30pm. You'll learn everything you need to know about how to integrate Push notifications &amp; Push Chat to enhance your protocols UX.
+#Web3 #PUSH #BUIDL</t>
+  </si>
+  <si>
+    <t>Day 1 of #100DaysOfCodeLW3 with 1 minute left before it turns into day 2 here (Central US Timezone :D ) 
+What did I do for today's #100DaysOfCode? I brushed up on some Solana dev, did some Rust troubleshooting, and voila, Hello world program deployed!
+@LearnWeb3DAO https://t.co/TsPd87fIls</t>
+  </si>
+  <si>
+    <t>Daily Tweet Update 
+Day (1)of #100DaysOfCode with @LearnWeb3DAO 
+1. It made me started my freshman course
+2. Very knowledgeable and outstanding 
+3. Also got familiar with Javascripts https://t.co/m4ID4O0g3v</t>
   </si>
   <si>
     <t>Day 2 of the #100DaysOfCode with @LearnWeb3DAO. went back to my freshman course and almost done
@@ -718,48 +1368,19 @@
 #100daysofcoding https://t.co/gf2V7qHxi9</t>
   </si>
   <si>
-    <t>Day 5 of #100daysofcode w/ 
+    <t>Call for builders 🤙 
+Push protocol partners with LearnWeb3DAO’s for $PUSH challenge
+The workshop will go live on Jan 26 where you can learn everything about integrating Push notification &amp; Push chat to enhance your protocols' UX 
+#100DaysofCode #PushProtocol</t>
+  </si>
+  <si>
+    <t>Day 27 of #100daysofcode w/ 
 @LearnWeb3DAO
-Completed a practice part module in js @scrimba 
-Explored ethereum documentation about decentralized storage.
+Revised react concepts
 #100DaysofCodeLW3</t>
   </si>
   <si>
-    <t>I'm gonna joining the #100daysofcode challenge with the my favourite @LearnWeb3DAO community! 
-Want to be web 3 developer ? 
-Upgrade your skills ?
-Join us here👇
-https://t.co/OXxvdQ0rEH
-We all will be focusing on Web3 development for 100 days!
-#100DaysofCodeLW3 LFG 💥</t>
-  </si>
-  <si>
-    <t>Daily Update Tweet: 
-Day 1 of #100daysofcode @LearnWeb3DAO
-1. Blockchain user state
-2. Tree Data structures 
-3. Blockchain Data storage 
-#100DaysofCodeLW3</t>
-  </si>
-  <si>
-    <t>Tambien estamos haciendo 
-#100DaysOfCode  w/ @LearnWeb3DAO
-así que si les interesa les voy mostrando mis avances en la plataforma
-como el De-Fi Exchange que creamos en el segundo nivel 💪 https://t.co/Vp6g8DGmDh</t>
-  </si>
-  <si>
-    <t>@LearnWeb3DAO 
-Nice work @NicholasJackm10! 💪 You're making great progress with your #100daysofcode. Keep up the good work! 🔥</t>
-  </si>
-  <si>
-    <t>i will update my 100days thread with @LearnWeb3DAO for the next 100 days  
-Day [1] of #100daysofcode 
-#100DaysOfCode https://t.co/fkVNz3t8HV</t>
-  </si>
-  <si>
-    <t>Day 1 of #100DaysOfCodeLW3 with 1 minute left before it turns into day 2 here (Central US Timezone :D ) 
-What did I do for today's #100DaysOfCode? I brushed up on some Solana dev, did some Rust troubleshooting, and voila, Hello world program deployed!
-@LearnWeb3DAO https://t.co/TsPd87fIls</t>
+    <t>@Gayathri1903 @LearnWeb3DAO How can I take part in #100DaysOfCode with @LearnWeb3DAO ?</t>
   </si>
   <si>
     <t>Everyone participating in  #100DaysOfCode .
@@ -769,39 +1390,22 @@
 @LearnWeb3DAO to the moon and beyond 🚀</t>
   </si>
   <si>
-    <t>@awesamarth_ @LearnWeb3DAO Congrats buddy💯🚀
-I am also thinking of starting #100DaysOfCode</t>
+    <t>@awesamarth_ @LearnWeb3DAO Great consistency brother. I am also going to start #100DaysOfCode from tomorrow</t>
+  </si>
+  <si>
+    <t>Not exactly day 1 but we'll start the challenge here.
+I still need more practice with recursion cause this problem took me 45 minutes😭
+@LearnWeb3DAO 
+#100DaysOfCode https://t.co/VYNKtq5zav</t>
   </si>
   <si>
     <t>Day 1 of #100daysofcode w/ @LearnWeb3DAO
-1. Going to work on Python (started awhile back but fell off and haven't done any work in months and never really committed or had any accountability)
-2. Created Github account and forked the 100 days of code log</t>
-  </si>
-  <si>
-    <t>Yayyy! I completed the Intro to Programming lesson on @LearnWeb3DAO with a perfect score! 
-Day 1 of #100daysofcode
-#100daysofdayscodeLW3
-What are you waiting for? Join me in learning web3 at https://t.co/Um2z8sXVn0</t>
-  </si>
-  <si>
-    <t>I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community.
-We'll be focusing on Web3 development for 100 days.
-Join us here:
-https://t.co/uEHyJj3Nva
-#100DaysofCodeLW3</t>
+From LW3's Freshman track
+Taking it slow.
+#100DaysofCodeLW3 https://t.co/Dg9MDH8s3t</t>
   </si>
   <si>
     <t>Excited to start 100daysofcode with my fav @LearnWeb3DAO ✨✨✨</t>
-  </si>
-  <si>
-    <t>@nithinchandranp @LearnWeb3DAO Wish you all the best in your 100 days of code Nithin.</t>
-  </si>
-  <si>
-    <t>Daily Tweet Update 
-Day (1)of #100DaysOfCode with @LearnWeb3DAO 
-1. It made me started my freshman course
-2. Very knowledgeable and outstanding 
-3. Also got familiar with Javascripts https://t.co/m4ID4O0g3v</t>
   </si>
   <si>
     <t>I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community! 💻
@@ -811,247 +1415,456 @@
 #100DaysofCodeLW3</t>
   </si>
   <si>
-    <t>@Radhey_Radhey_1 @pytwt3 @LearnWeb3DAO Lol, awesome! Keep up the good work! #100daysofcode</t>
-  </si>
-  <si>
-    <t>@awesamarth_ @LearnWeb3DAO Great consistency brother. I am also going to start #100DaysOfCode from tomorrow</t>
-  </si>
-  <si>
-    <t>https://twitter.com/AamirUsmani1552/status/1614640080185970688</t>
-  </si>
-  <si>
-    <t>https://twitter.com/a20zCrypto/status/1614478384922497024</t>
-  </si>
-  <si>
-    <t>https://twitter.com/nandagopan__/status/1614683329974145025</t>
-  </si>
-  <si>
-    <t>https://twitter.com/nithinchandranp/status/1614605118351212549</t>
-  </si>
-  <si>
-    <t>https://twitter.com/2xprathamesh/status/1614684482979889153</t>
-  </si>
-  <si>
-    <t>https://twitter.com/ChaffieRN/status/1614650971295981570</t>
-  </si>
-  <si>
-    <t>https://twitter.com/HanabiPlug/status/1614655804052758528</t>
-  </si>
-  <si>
-    <t>https://twitter.com/Maitrayeedas9/status/1614660584427114496</t>
-  </si>
-  <si>
-    <t>https://twitter.com/dazkool69/status/1614604814272561152</t>
-  </si>
-  <si>
-    <t>https://twitter.com/manoharsspace/status/1614677295146598400</t>
-  </si>
-  <si>
-    <t>https://twitter.com/kushagrasarathe/status/1614649072459321344</t>
-  </si>
-  <si>
-    <t>https://twitter.com/RitikkAgarwalll/status/1614528798254563331</t>
-  </si>
-  <si>
-    <t>https://twitter.com/blagoichelovek/status/1614680499544268800</t>
-  </si>
-  <si>
-    <t>https://twitter.com/Jbusta2103/status/1614444316210122756</t>
-  </si>
-  <si>
-    <t>https://twitter.com/_0x416B68696C_/status/1614477732532084737</t>
-  </si>
-  <si>
-    <t>https://twitter.com/karthik___gk/status/1614642212415111168</t>
-  </si>
-  <si>
-    <t>https://twitter.com/yc_crypto/status/1614620500885372928</t>
-  </si>
-  <si>
-    <t>https://twitter.com/vundnido/status/1614457175773954059</t>
-  </si>
-  <si>
-    <t>https://twitter.com/seamlesslyjj/status/1614118692522004480</t>
-  </si>
-  <si>
-    <t>https://twitter.com/TiwariAnkitb/status/1614306646624440323</t>
-  </si>
-  <si>
-    <t>https://twitter.com/Radhey_Radhey_1/status/1614296269341720577</t>
-  </si>
-  <si>
-    <t>https://twitter.com/DexterMatis0489/status/1614480102628155393</t>
-  </si>
-  <si>
-    <t>https://twitter.com/NicholasJackm10/status/1614337878850666496</t>
-  </si>
-  <si>
-    <t>https://twitter.com/Zartaj20031/status/1614667211808940034</t>
-  </si>
-  <si>
-    <t>https://twitter.com/ArshiaZojaji/status/1614678971832049666</t>
-  </si>
-  <si>
-    <t>https://twitter.com/gornyhor/status/1614526084195794945</t>
-  </si>
-  <si>
-    <t>https://twitter.com/VaibhavSinghDev/status/1614367190693859332</t>
-  </si>
-  <si>
-    <t>https://twitter.com/tanja_codes/status/1614359956030988292</t>
-  </si>
-  <si>
-    <t>https://twitter.com/cjski_web3/status/1614392891249463296</t>
-  </si>
-  <si>
-    <t>https://twitter.com/gossdotinc/status/1614337557713780737</t>
-  </si>
-  <si>
-    <t>https://twitter.com/Talkweb03/status/1614351790626988037</t>
-  </si>
-  <si>
-    <t>https://twitter.com/PandeyAshwini9/status/1614314370712100864</t>
-  </si>
-  <si>
-    <t>https://twitter.com/ichabod_721/status/1614428497379819525</t>
-  </si>
-  <si>
-    <t>https://twitter.com/Bs_Alade/status/1614405461897535488</t>
-  </si>
-  <si>
-    <t>https://twitter.com/outerspacesoph/status/1614442787491164163</t>
-  </si>
-  <si>
-    <t>https://twitter.com/TheRealOkanisis/status/1614414344594554880</t>
-  </si>
-  <si>
-    <t>https://twitter.com/web3Learning2/status/1614646665847128064</t>
-  </si>
-  <si>
-    <t>https://twitter.com/Roq411/status/1614439893916155904</t>
-  </si>
-  <si>
-    <t>https://twitter.com/midesofek/status/1614395213749039104</t>
-  </si>
-  <si>
-    <t>https://twitter.com/Justacanuk81/status/1614314318065029120</t>
-  </si>
-  <si>
-    <t>https://twitter.com/Uchewizzy_31/status/1614399242163863555</t>
+    <t>Day 19 of #100daysofcode w/ 
+@LearnWeb3DAO
+Explored @pushprotocol documentation. 
+working on react project.
+#100DaysofCodeLW3</t>
+  </si>
+  <si>
+    <t>A year ago on this day we started pair programming on the @LearnWeb3DAO discord server and the rest is history.
+Super happy to see the rest of the community take similar initiatives such as #100DaysOfCode and grow together.</t>
+  </si>
+  <si>
+    <t>i will update my 100days thread with @LearnWeb3DAO for the next 100 days  
+Day [1] of #100daysofcode 
+#100DaysOfCode https://t.co/fkVNz3t8HV</t>
+  </si>
+  <si>
+    <t>@nithinchandranp @LearnWeb3DAO Wish you all the best in your 100 days of code Nithin.</t>
+  </si>
+  <si>
+    <t>Day 1 of #100daysofcode w/ @LearnWeb3DAO
+1. Going to work on Python (started awhile back but fell off and haven't done any work in months and never really committed or had any accountability)
+2. Created Github account and forked the 100 days of code log</t>
+  </si>
+  <si>
+    <t>I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community! 💻
+We'll be focusing on Web3 development for 100 days!
+Join us here👇
+https://t.co/RxFgo8N40x
+#100DaysofCodeLW3 
+—&amp;gt; Next 🎯 300 Days 🔥 #365DaysOfCode</t>
+  </si>
+  <si>
+    <t>I'm joining the #100daysofcode challenge with the @LearnWeb3DAO community! 💻</t>
+  </si>
+  <si>
+    <t>https://twitter.com/ChaffieRN/status/1627693738259537922</t>
+  </si>
+  <si>
+    <t>https://twitter.com/dazkool69/status/1627744995372580865</t>
+  </si>
+  <si>
+    <t>https://twitter.com/HanabiPlug/status/1627750222926385182</t>
+  </si>
+  <si>
+    <t>https://twitter.com/nithinchandranp/status/1627726751018422272</t>
+  </si>
+  <si>
+    <t>https://twitter.com/a20zCrypto/status/1627567478271516672</t>
+  </si>
+  <si>
+    <t>https://twitter.com/tanja_codes/status/1627773196295458851</t>
+  </si>
+  <si>
+    <t>https://twitter.com/gossdotinc/status/1627740305205362688</t>
+  </si>
+  <si>
+    <t>https://twitter.com/karthik___gk/status/1627700957223215104</t>
+  </si>
+  <si>
+    <t>https://twitter.com/cjski_web3/status/1627795716931190785</t>
+  </si>
+  <si>
+    <t>https://twitter.com/AamirUsmani1552/status/1626603440460935169</t>
+  </si>
+  <si>
+    <t>https://twitter.com/TheRealOkanisis/status/1627577459796480000</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Jbusta2103/status/1627549324618919937</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Zartaj20031/status/1627009575353303043</t>
+  </si>
+  <si>
+    <t>https://twitter.com/outerspacesoph/status/1627124037918003206</t>
+  </si>
+  <si>
+    <t>https://twitter.com/RitikkAgarwalll/status/1627377429177335809</t>
+  </si>
+  <si>
+    <t>https://twitter.com/ankit7241/status/1627517669716148225</t>
+  </si>
+  <si>
+    <t>https://twitter.com/NicholasJackm10/status/1627810312731922432</t>
+  </si>
+  <si>
+    <t>https://twitter.com/yc_crypto/status/1627774109928116253</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Uchewizzy_31/status/1627761837520437249</t>
+  </si>
+  <si>
+    <t>https://twitter.com/_Ayoola01/status/1627796700285878275</t>
+  </si>
+  <si>
+    <t>https://twitter.com/2xprathamesh/status/1625178447361503233</t>
+  </si>
+  <si>
+    <t>https://twitter.com/manoharsspace/status/1624085796268707851</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Gayathri1903/status/1627689732082921472</t>
+  </si>
+  <si>
+    <t>https://twitter.com/nandagopan__/status/1627714033695735809</t>
+  </si>
+  <si>
+    <t>https://twitter.com/PandeyAshwini9/status/1623744688896487424</t>
+  </si>
+  <si>
+    <t>https://twitter.com/TiwariAnkitb/status/1623741343829983233</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Kazim_walid/status/1627769065073791007</t>
+  </si>
+  <si>
+    <t>https://twitter.com/midesofek/status/1627804777307414529</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Talkweb03/status/1626379199429677056</t>
+  </si>
+  <si>
+    <t>https://twitter.com/kushagrasarathe/status/1623581710272319488</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Mr_MicDaniel/status/1627780296736137217</t>
+  </si>
+  <si>
+    <t>https://twitter.com/vundnido/status/1622816174424862722</t>
+  </si>
+  <si>
+    <t>https://twitter.com/naps_thelma/status/1627439906661232641</t>
+  </si>
+  <si>
+    <t>https://twitter.com/aryc_dev/status/1622443647022268423</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Bs_Alade/status/1622084034007339008</t>
+  </si>
+  <si>
+    <t>https://twitter.com/gornyhor/status/1622122166421520384</t>
+  </si>
+  <si>
+    <t>https://twitter.com/DexterMatis0489/status/1624266044461273088</t>
+  </si>
+  <si>
+    <t>https://twitter.com/itorobrown814/status/1625206671071973410</t>
+  </si>
+  <si>
+    <t>https://twitter.com/stormyymrots/status/1627729369555959814</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Ketan_14n/status/1627727682913067011</t>
+  </si>
+  <si>
+    <t>https://twitter.com/VaibhavSinghDev/status/1621667602543308800</t>
+  </si>
+  <si>
+    <t>https://twitter.com/blagoichelovek/status/1622657430889930765</t>
+  </si>
+  <si>
+    <t>https://twitter.com/web3Learning2/status/1627763846931795986</t>
+  </si>
+  <si>
+    <t>https://twitter.com/chinedu_sol/status/1620572462957359104</t>
+  </si>
+  <si>
+    <t>https://twitter.com/ActivateGlacier/status/1627484440308899840</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Harshpatil03/status/1627748114563207168</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Radhey_Radhey_1/status/1619013971952144384</t>
+  </si>
+  <si>
+    <t>https://twitter.com/iamanilmhj/status/1627731695565950976</t>
+  </si>
+  <si>
+    <t>https://twitter.com/WhiteR4bbitt/status/1625378160950005760</t>
+  </si>
+  <si>
+    <t>https://twitter.com/panditdhamdhere/status/1626937487410225155</t>
+  </si>
+  <si>
+    <t>https://twitter.com/0xSan3/status/1618954967670468608</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Justacanuk81/status/1620627779112038407</t>
+  </si>
+  <si>
+    <t>https://twitter.com/_0x416B68696C_/status/1623919979199606784</t>
+  </si>
+  <si>
+    <t>https://twitter.com/3aglefly/status/1625218211422560256</t>
+  </si>
+  <si>
+    <t>https://twitter.com/ShivamBarke/status/1627707264328163328</t>
+  </si>
+  <si>
+    <t>https://twitter.com/binary_floyd/status/1618357687795994625</t>
+  </si>
+  <si>
+    <t>https://twitter.com/rav3kid/status/1619749487160999936</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Maitrayeedas9/status/1616097087837605893</t>
+  </si>
+  <si>
+    <t>https://twitter.com/seamlesslyjj/status/1617003273164029954</t>
+  </si>
+  <si>
+    <t>https://twitter.com/SimonFUTURE2/status/1619517420594683904</t>
+  </si>
+  <si>
+    <t>https://twitter.com/ShivDixit21/status/1627373935091408906</t>
+  </si>
+  <si>
+    <t>https://twitter.com/ArshiaZojaji/status/1615818892282302464</t>
+  </si>
+  <si>
+    <t>https://twitter.com/ThirdMistrust/status/1627788026003787779</t>
+  </si>
+  <si>
+    <t>https://twitter.com/ichabod_721/status/1615473506162024472</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Roq411/status/1615887809075896320</t>
+  </si>
+  <si>
+    <t>https://twitter.com/singh_vaibhav08/status/1625212578040528896</t>
+  </si>
+  <si>
+    <t>https://twitter.com/pushprotocol/status/1623387148245147655</t>
+  </si>
+  <si>
+    <t>https://twitter.com/awesamarth_/status/1616698876978950146</t>
   </si>
   <si>
     <t>https://twitter.com/saurabh17999/status/1613938544812388353</t>
   </si>
   <si>
-    <t>https://twitter.com/_Ayoola01/status/1614386995597553665</t>
-  </si>
-  <si>
-    <t>https://twitter.com/itorobrown814/status/1613981231343087618</t>
-  </si>
-  <si>
-    <t>https://twitter.com/binary_floyd/status/1614049695550308352</t>
-  </si>
-  <si>
-    <t>https://twitter.com/chinedu_sol/status/1614386211329646593</t>
-  </si>
-  <si>
-    <t>https://twitter.com/MakumbaOscar/status/1613575704519610374</t>
-  </si>
-  <si>
-    <t>https://twitter.com/0xCylax/status/1613592319797907456</t>
+    <t>https://twitter.com/MakumbaOscar/status/1615742071096098817</t>
+  </si>
+  <si>
+    <t>https://twitter.com/MarkusEicher70/status/1627490510507057154</t>
+  </si>
+  <si>
+    <t>https://twitter.com/__MikeDrop__/status/1613630458641670145</t>
+  </si>
+  <si>
+    <t>https://twitter.com/NyambegaBray/status/1624066980507533313</t>
+  </si>
+  <si>
+    <t>https://twitter.com/0xChinedu/status/1621641786325090304</t>
+  </si>
+  <si>
+    <t>https://twitter.com/sawxnhere/status/1625199042757296129</t>
+  </si>
+  <si>
+    <t>https://twitter.com/josephomotade0/status/1615174693576708096</t>
   </si>
   <si>
     <t>https://twitter.com/audaciousSneha/status/1614359155908964353</t>
   </si>
   <si>
-    <t>https://twitter.com/__MikeDrop__/status/1613630458641670145</t>
-  </si>
-  <si>
-    <t>https://twitter.com/WhiteR4bbitt/status/1614470509030432769</t>
-  </si>
-  <si>
-    <t>https://twitter.com/awesamarth_/status/1614536345137082368</t>
-  </si>
-  <si>
-    <t>https://twitter.com/ankit7241/status/1613599231369154560</t>
-  </si>
-  <si>
-    <t>https://twitter.com/SimonFUTURE2/status/1613408204268130306</t>
+    <t>https://twitter.com/Ayodeji7111/status/1622454409144803328</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Vaibhavs_twt/status/1622288196913741824</t>
+  </si>
+  <si>
+    <t>https://twitter.com/JackD_eth/status/1626977194605150208</t>
+  </si>
+  <si>
+    <t>https://twitter.com/naitik_shrma/status/1621968740765306880</t>
   </si>
   <si>
     <t>https://twitter.com/SumrenderS/status/1613239398560321537</t>
   </si>
   <si>
-    <t>https://twitter.com/aryc_dev/status/1613597442989252608</t>
-  </si>
-  <si>
-    <t>https://twitter.com/josephomotade0/status/1613796796698099712</t>
-  </si>
-  <si>
-    <t>https://twitter.com/rav3kid/status/1612857411953647617</t>
+    <t>https://twitter.com/sriram_s_s/status/1625570858860441600</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Saurabhh_Web3/status/1621123915975397376</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Agrim_Sharma174/status/1627722379672829958</t>
+  </si>
+  <si>
+    <t>https://twitter.com/CryptoAxiom/status/1626576480343056384</t>
+  </si>
+  <si>
+    <t>https://twitter.com/lite_745/status/1624836591251251203</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Robertsteacher1/status/1625147799338889222</t>
+  </si>
+  <si>
+    <t>https://twitter.com/rahul3526/status/1622603260111765505</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Ch8992/status/1627773195813093376</t>
+  </si>
+  <si>
+    <t>https://twitter.com/temple_snowden/status/1615819844720500738</t>
+  </si>
+  <si>
+    <t>https://twitter.com/muqtadirsandha/status/1622242004771172359</t>
+  </si>
+  <si>
+    <t>https://twitter.com/jadernalia/status/1621536567880720384</t>
+  </si>
+  <si>
+    <t>https://twitter.com/RobertLeeSaund/status/1624060622639108096</t>
+  </si>
+  <si>
+    <t>https://twitter.com/CharanSinghTo18/status/1613990328331304961</t>
+  </si>
+  <si>
+    <t>https://twitter.com/LarryCutts6/status/1621184633126719488</t>
+  </si>
+  <si>
+    <t>https://twitter.com/samueloh99/status/1624006564100145153</t>
+  </si>
+  <si>
+    <t>https://twitter.com/mokhteeb74/status/1620020054602682368</t>
+  </si>
+  <si>
+    <t>https://twitter.com/tajamul9342/status/1617529164327972872</t>
+  </si>
+  <si>
+    <t>https://twitter.com/topagentmike007/status/1621478105587277825</t>
+  </si>
+  <si>
+    <t>https://twitter.com/wilbermayflore1/status/1620613505442529280</t>
+  </si>
+  <si>
+    <t>https://twitter.com/thehapadev/status/1620370133322715136</t>
+  </si>
+  <si>
+    <t>https://twitter.com/DrMelvaMitchel1/status/1625510174734811136</t>
+  </si>
+  <si>
+    <t>https://twitter.com/NG8world/status/1618509787863580672</t>
+  </si>
+  <si>
+    <t>https://twitter.com/avi0_07/status/1613446417732747264</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Web3_Manu/status/1621002810832867328</t>
+  </si>
+  <si>
+    <t>https://twitter.com/mahesh_19w/status/1612845702006341633</t>
+  </si>
+  <si>
+    <t>https://twitter.com/ShivamJ0502/status/1622611506155393024</t>
+  </si>
+  <si>
+    <t>https://twitter.com/greg_aloi/status/1624060623318581248</t>
+  </si>
+  <si>
+    <t>https://twitter.com/0x0DeeDee/status/1621538774617583623</t>
+  </si>
+  <si>
+    <t>https://twitter.com/AaroshYadav/status/1613997783328952330</t>
+  </si>
+  <si>
+    <t>https://twitter.com/YashSolanki_/status/1624903587578130432</t>
+  </si>
+  <si>
+    <t>https://twitter.com/devarakonda9908/status/1613996069632806946</t>
+  </si>
+  <si>
+    <t>https://twitter.com/0_1inspiration/status/1612621616374075394</t>
+  </si>
+  <si>
+    <t>https://twitter.com/SamuelSojin/status/1613325565167284225</t>
+  </si>
+  <si>
+    <t>https://twitter.com/02b2YBH/status/1622963994209255425</t>
+  </si>
+  <si>
+    <t>https://twitter.com/WiliBastar/status/1620721812060647426</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Sergioconstant_/status/1614030035559788544</t>
+  </si>
+  <si>
+    <t>https://twitter.com/imkunaal02/status/1618599990355701760</t>
+  </si>
+  <si>
+    <t>https://twitter.com/CuddleofDeath/status/1612690686393843712</t>
+  </si>
+  <si>
+    <t>https://twitter.com/MayorPella01/status/1612765966630256640</t>
   </si>
   <si>
     <t>https://twitter.com/Alutasam/status/1612932154542923780</t>
   </si>
   <si>
-    <t>https://twitter.com/CharanSinghTo18/status/1613990328331304961</t>
-  </si>
-  <si>
-    <t>https://twitter.com/panditdhamdhere/status/1612497998889779200</t>
-  </si>
-  <si>
-    <t>https://twitter.com/naps_thelma/status/1612573766097293334</t>
-  </si>
-  <si>
-    <t>https://twitter.com/devarakonda9908/status/1613996069632806946</t>
-  </si>
-  <si>
-    <t>https://twitter.com/AaroshYadav/status/1613997783328952330</t>
-  </si>
-  <si>
-    <t>https://twitter.com/Sergioconstant_/status/1614030035559788544</t>
-  </si>
-  <si>
-    <t>https://twitter.com/SamuelSojin/status/1613325565167284225</t>
+    <t>https://twitter.com/cryptowithabhi/status/1617786429572284419</t>
+  </si>
+  <si>
+    <t>https://twitter.com/LoogtanP/status/1621958812490940416</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Varunx10/status/1618447041344212992</t>
+  </si>
+  <si>
+    <t>https://twitter.com/aahiknsv/status/1612881430153154560</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Dev92rishi/status/1614581597566820352</t>
+  </si>
+  <si>
+    <t>https://twitter.com/bj8697/status/1623182667440173056</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Vaibhavs_8/status/1621667602543308800</t>
+  </si>
+  <si>
+    <t>https://twitter.com/saikrishna2023/status/1627706112329027585</t>
+  </si>
+  <si>
+    <t>https://twitter.com/shikkhar_/status/1612682573511282693</t>
+  </si>
+  <si>
+    <t>https://twitter.com/de_ddon/status/1612841506041102337</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Mind56045188/status/1619795155430838272</t>
+  </si>
+  <si>
+    <t>https://twitter.com/KhanAbbas201/status/1615553537274163201</t>
   </si>
   <si>
     <t>https://twitter.com/El_Jardon/status/1613327638981926912</t>
   </si>
   <si>
-    <t>https://twitter.com/CuddleofDeath/status/1612690686393843712</t>
-  </si>
-  <si>
-    <t>https://twitter.com/aahiknsv/status/1612881430153154560</t>
-  </si>
-  <si>
-    <t>https://twitter.com/avi0_07/status/1613446417732747264</t>
+    <t>https://twitter.com/SsekiwalaC/status/1612292399325118464</t>
   </si>
   <si>
     <t>https://twitter.com/IDoNutSeeMoney/status/1612894504134258689</t>
   </si>
   <si>
-    <t>https://twitter.com/mahesh_19w/status/1612845702006341633</t>
-  </si>
-  <si>
-    <t>https://twitter.com/0_1inspiration/status/1612621616374075394</t>
-  </si>
-  <si>
-    <t>https://twitter.com/shikkhar_/status/1612682573511282693</t>
-  </si>
-  <si>
-    <t>https://twitter.com/SsekiwalaC/status/1612292399325118464</t>
-  </si>
-  <si>
-    <t>https://twitter.com/MayorPella01/status/1612765966630256640</t>
-  </si>
-  <si>
-    <t>https://twitter.com/de_ddon/status/1612841506041102337</t>
-  </si>
-  <si>
-    <t>https://twitter.com/shobhitexe/status/1613205884364099585</t>
-  </si>
-  <si>
-    <t>https://twitter.com/Dev92rishi/status/1614581597566820352</t>
+    <t>https://twitter.com/rohitscode/status/1627654654724276224</t>
+  </si>
+  <si>
+    <t>https://twitter.com/Vaibhavtwts/status/1627648678306643969</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +2235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1447,16 +2260,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>168</v>
+        <v>314</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1464,16 +2277,16 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>180</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>169</v>
+        <v>315</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1481,16 +2294,16 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>181</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>170</v>
+        <v>316</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1498,16 +2311,16 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>182</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>171</v>
+        <v>317</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1515,16 +2328,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>183</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>172</v>
+        <v>318</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1532,16 +2345,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>173</v>
+        <v>319</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1549,16 +2362,16 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>174</v>
+        <v>320</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1566,16 +2379,16 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>175</v>
+        <v>321</v>
       </c>
       <c r="E9">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1583,33 +2396,33 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>187</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>176</v>
+        <v>322</v>
       </c>
       <c r="E10">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>188</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>177</v>
+        <v>323</v>
       </c>
       <c r="E11">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1617,16 +2430,16 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>189</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>178</v>
+        <v>324</v>
       </c>
       <c r="E12">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1634,67 +2447,67 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>190</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>179</v>
+        <v>325</v>
       </c>
       <c r="E13">
-        <v>6</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>191</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>180</v>
+        <v>326</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>192</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>181</v>
+        <v>327</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>182</v>
+        <v>328</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1702,16 +2515,16 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>194</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>183</v>
+        <v>329</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1719,16 +2532,16 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>195</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>184</v>
+        <v>330</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1736,101 +2549,101 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>196</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>185</v>
+        <v>331</v>
       </c>
       <c r="E19">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>197</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>186</v>
+        <v>332</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>187</v>
+        <v>333</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>199</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>188</v>
+        <v>334</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>200</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>189</v>
+        <v>335</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>201</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>190</v>
+        <v>336</v>
       </c>
       <c r="E24">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1838,84 +2651,84 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>202</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>191</v>
+        <v>337</v>
       </c>
       <c r="E25">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>203</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>192</v>
+        <v>338</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>204</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>193</v>
+        <v>339</v>
       </c>
       <c r="E27">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>205</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>194</v>
+        <v>340</v>
       </c>
       <c r="E28">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>206</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>195</v>
+        <v>341</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1923,424 +2736,424 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>207</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>196</v>
+        <v>342</v>
       </c>
       <c r="E30">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>208</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>197</v>
+        <v>343</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>198</v>
+        <v>344</v>
       </c>
       <c r="E32">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>210</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>199</v>
+        <v>345</v>
       </c>
       <c r="E33">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>123</v>
+        <v>211</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>200</v>
+        <v>346</v>
       </c>
       <c r="E34">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="C35" t="s">
-        <v>124</v>
+        <v>212</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>201</v>
+        <v>347</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>213</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>202</v>
+        <v>348</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C37" t="s">
-        <v>126</v>
+        <v>214</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>203</v>
+        <v>349</v>
       </c>
       <c r="E37">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>127</v>
+        <v>215</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>204</v>
+        <v>350</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
-        <v>128</v>
+        <v>216</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>205</v>
+        <v>351</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="C40" t="s">
-        <v>129</v>
+        <v>217</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>206</v>
+        <v>352</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="C41" t="s">
-        <v>130</v>
+        <v>218</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>207</v>
+        <v>353</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="C42" t="s">
-        <v>131</v>
+        <v>219</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>208</v>
+        <v>354</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>220</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>209</v>
+        <v>355</v>
       </c>
       <c r="E43">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="C44" t="s">
-        <v>133</v>
+        <v>221</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>210</v>
+        <v>356</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>211</v>
+        <v>357</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="C46" t="s">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>212</v>
+        <v>358</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="C47" t="s">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>213</v>
+        <v>359</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="C48" t="s">
-        <v>137</v>
+        <v>225</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>214</v>
+        <v>360</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>226</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>215</v>
+        <v>361</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
-        <v>139</v>
+        <v>227</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>216</v>
+        <v>362</v>
       </c>
       <c r="E50">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="C51" t="s">
-        <v>140</v>
+        <v>228</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>217</v>
+        <v>363</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="C52" t="s">
-        <v>141</v>
+        <v>229</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>218</v>
+        <v>364</v>
       </c>
       <c r="E52">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="C53" t="s">
-        <v>142</v>
+        <v>230</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>219</v>
+        <v>365</v>
       </c>
       <c r="E53">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="C54" t="s">
-        <v>143</v>
+        <v>231</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>220</v>
+        <v>366</v>
       </c>
       <c r="E54">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2348,203 +3161,203 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C55" t="s">
-        <v>144</v>
+        <v>232</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>221</v>
+        <v>367</v>
       </c>
       <c r="E55">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="C56" t="s">
-        <v>145</v>
+        <v>233</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>222</v>
+        <v>368</v>
       </c>
       <c r="E56">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="C57" t="s">
-        <v>146</v>
+        <v>234</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>223</v>
+        <v>369</v>
       </c>
       <c r="E57">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C58" t="s">
-        <v>147</v>
+        <v>235</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>224</v>
+        <v>370</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59" t="s">
+        <v>97</v>
+      </c>
+      <c r="C59" t="s">
+        <v>236</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E59">
         <v>10</v>
-      </c>
-      <c r="B59" t="s">
-        <v>69</v>
-      </c>
-      <c r="C59" t="s">
-        <v>148</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E59">
-        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="C60" t="s">
-        <v>149</v>
+        <v>237</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>226</v>
+        <v>372</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="C61" t="s">
-        <v>150</v>
+        <v>238</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>227</v>
+        <v>373</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="C62" t="s">
-        <v>151</v>
+        <v>239</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>228</v>
+        <v>374</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B63" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="C63" t="s">
-        <v>152</v>
+        <v>240</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>229</v>
+        <v>375</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="C64" t="s">
-        <v>150</v>
+        <v>241</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>230</v>
+        <v>376</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
+        <v>23</v>
+      </c>
+      <c r="B65" t="s">
+        <v>103</v>
+      </c>
+      <c r="C65" t="s">
+        <v>242</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E65">
         <v>7</v>
-      </c>
-      <c r="B65" t="s">
-        <v>75</v>
-      </c>
-      <c r="C65" t="s">
-        <v>150</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E65">
-        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
+        <v>20</v>
+      </c>
+      <c r="B66" t="s">
+        <v>104</v>
+      </c>
+      <c r="C66" t="s">
+        <v>243</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E66">
         <v>7</v>
-      </c>
-      <c r="B66" t="s">
-        <v>76</v>
-      </c>
-      <c r="C66" t="s">
-        <v>153</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E66">
-        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2552,236 +3365,1256 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C67" t="s">
-        <v>154</v>
+        <v>244</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>233</v>
+        <v>379</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B68" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C68" t="s">
-        <v>155</v>
+        <v>245</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>234</v>
+        <v>380</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C69" t="s">
-        <v>156</v>
+        <v>246</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>235</v>
+        <v>381</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B70" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C70" t="s">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>236</v>
+        <v>382</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B71" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="C71" t="s">
-        <v>158</v>
+        <v>248</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>237</v>
+        <v>383</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B72" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="C72" t="s">
-        <v>159</v>
+        <v>249</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>238</v>
+        <v>384</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B73" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="C73" t="s">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>239</v>
+        <v>385</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C74" t="s">
-        <v>161</v>
+        <v>251</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>240</v>
+        <v>386</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B75" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="C75" t="s">
-        <v>162</v>
+        <v>252</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>241</v>
+        <v>387</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="C76" t="s">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>242</v>
+        <v>388</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B77" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C77" t="s">
-        <v>164</v>
+        <v>254</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>243</v>
+        <v>389</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B78" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="C78" t="s">
-        <v>165</v>
+        <v>255</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>244</v>
+        <v>390</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="C79" t="s">
-        <v>166</v>
+        <v>256</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>245</v>
+        <v>391</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
+        <v>12</v>
+      </c>
+      <c r="B80" t="s">
+        <v>118</v>
+      </c>
+      <c r="C80" t="s">
+        <v>257</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E80">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>6</v>
+      </c>
+      <c r="B81" t="s">
+        <v>119</v>
+      </c>
+      <c r="C81" t="s">
+        <v>258</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E81">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" t="s">
+        <v>120</v>
+      </c>
+      <c r="C82" t="s">
+        <v>259</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" t="s">
+        <v>121</v>
+      </c>
+      <c r="C83" t="s">
+        <v>260</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E83">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" t="s">
+        <v>122</v>
+      </c>
+      <c r="C84" t="s">
+        <v>261</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E84">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>31</v>
+      </c>
+      <c r="B85" t="s">
+        <v>123</v>
+      </c>
+      <c r="C85" t="s">
+        <v>262</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
         <v>5</v>
       </c>
-      <c r="B80" t="s">
-        <v>90</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="B86" t="s">
+        <v>124</v>
+      </c>
+      <c r="C86" t="s">
+        <v>263</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E86">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>6</v>
+      </c>
+      <c r="B87" t="s">
+        <v>125</v>
+      </c>
+      <c r="C87" t="s">
+        <v>264</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>32</v>
+      </c>
+      <c r="B88" t="s">
+        <v>126</v>
+      </c>
+      <c r="C88" t="s">
+        <v>265</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>8</v>
+      </c>
+      <c r="B89" t="s">
+        <v>127</v>
+      </c>
+      <c r="C89" t="s">
+        <v>266</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>12</v>
+      </c>
+      <c r="B90" t="s">
+        <v>128</v>
+      </c>
+      <c r="C90" t="s">
+        <v>267</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>5</v>
+      </c>
+      <c r="B91" t="s">
+        <v>129</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>22</v>
+      </c>
+      <c r="B92" t="s">
+        <v>130</v>
+      </c>
+      <c r="C92" t="s">
+        <v>269</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>12</v>
+      </c>
+      <c r="B93" t="s">
+        <v>131</v>
+      </c>
+      <c r="C93" t="s">
+        <v>270</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>28</v>
+      </c>
+      <c r="B94" t="s">
+        <v>132</v>
+      </c>
+      <c r="C94" t="s">
+        <v>271</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>9</v>
+      </c>
+      <c r="B95" t="s">
+        <v>133</v>
+      </c>
+      <c r="C95" t="s">
+        <v>272</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>26</v>
+      </c>
+      <c r="B96" t="s">
+        <v>134</v>
+      </c>
+      <c r="C96" t="s">
+        <v>273</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>31</v>
+      </c>
+      <c r="B97" t="s">
+        <v>135</v>
+      </c>
+      <c r="C97" t="s">
+        <v>274</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>9</v>
+      </c>
+      <c r="B98" t="s">
+        <v>136</v>
+      </c>
+      <c r="C98" t="s">
+        <v>275</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>33</v>
+      </c>
+      <c r="B99" t="s">
+        <v>137</v>
+      </c>
+      <c r="C99" t="s">
+        <v>276</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>34</v>
+      </c>
+      <c r="B100" t="s">
+        <v>138</v>
+      </c>
+      <c r="C100" t="s">
+        <v>277</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>28</v>
+      </c>
+      <c r="B101" t="s">
+        <v>139</v>
+      </c>
+      <c r="C101" t="s">
+        <v>278</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B102" t="s">
+        <v>140</v>
+      </c>
+      <c r="C102" t="s">
+        <v>279</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>141</v>
+      </c>
+      <c r="C103" t="s">
+        <v>280</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
+        <v>8</v>
+      </c>
+      <c r="B104" t="s">
+        <v>142</v>
+      </c>
+      <c r="C104" t="s">
+        <v>281</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>35</v>
+      </c>
+      <c r="B105" t="s">
+        <v>143</v>
+      </c>
+      <c r="C105" t="s">
+        <v>282</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
+        <v>27</v>
+      </c>
+      <c r="B106" t="s">
+        <v>144</v>
+      </c>
+      <c r="C106" t="s">
+        <v>283</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
+        <v>31</v>
+      </c>
+      <c r="B107" t="s">
+        <v>145</v>
+      </c>
+      <c r="C107" t="s">
+        <v>284</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>36</v>
+      </c>
+      <c r="B108" t="s">
+        <v>146</v>
+      </c>
+      <c r="C108" t="s">
+        <v>285</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
+        <v>12</v>
+      </c>
+      <c r="B109" t="s">
+        <v>147</v>
+      </c>
+      <c r="C109" t="s">
+        <v>286</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>9</v>
+      </c>
+      <c r="B110" t="s">
+        <v>148</v>
+      </c>
+      <c r="C110" t="s">
+        <v>287</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>28</v>
+      </c>
+      <c r="B111" t="s">
+        <v>149</v>
+      </c>
+      <c r="C111" t="s">
+        <v>288</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>26</v>
+      </c>
+      <c r="B112" t="s">
+        <v>150</v>
+      </c>
+      <c r="C112" t="s">
+        <v>273</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
+        <v>32</v>
+      </c>
+      <c r="B113" t="s">
+        <v>151</v>
+      </c>
+      <c r="C113" t="s">
+        <v>289</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>26</v>
+      </c>
+      <c r="B114" t="s">
+        <v>152</v>
+      </c>
+      <c r="C114" t="s">
+        <v>273</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
+        <v>36</v>
+      </c>
+      <c r="B115" t="s">
+        <v>153</v>
+      </c>
+      <c r="C115" t="s">
+        <v>290</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" t="s">
+        <v>27</v>
+      </c>
+      <c r="B116" t="s">
+        <v>154</v>
+      </c>
+      <c r="C116" t="s">
+        <v>291</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" t="s">
+        <v>155</v>
+      </c>
+      <c r="C117" t="s">
+        <v>292</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" t="s">
+        <v>17</v>
+      </c>
+      <c r="B118" t="s">
+        <v>156</v>
+      </c>
+      <c r="C118" t="s">
+        <v>279</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" t="s">
+        <v>26</v>
+      </c>
+      <c r="B119" t="s">
+        <v>157</v>
+      </c>
+      <c r="C119" t="s">
+        <v>293</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" t="s">
+        <v>35</v>
+      </c>
+      <c r="B120" t="s">
+        <v>158</v>
+      </c>
+      <c r="C120" t="s">
+        <v>294</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" t="s">
+        <v>36</v>
+      </c>
+      <c r="B121" t="s">
+        <v>159</v>
+      </c>
+      <c r="C121" t="s">
+        <v>295</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" t="s">
+        <v>36</v>
+      </c>
+      <c r="B122" t="s">
+        <v>160</v>
+      </c>
+      <c r="C122" t="s">
+        <v>296</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" t="s">
+        <v>36</v>
+      </c>
+      <c r="B123" t="s">
+        <v>161</v>
+      </c>
+      <c r="C123" t="s">
+        <v>297</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" t="s">
+        <v>37</v>
+      </c>
+      <c r="B124" t="s">
+        <v>162</v>
+      </c>
+      <c r="C124" t="s">
+        <v>298</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" t="s">
+        <v>14</v>
+      </c>
+      <c r="B125" t="s">
+        <v>163</v>
+      </c>
+      <c r="C125" t="s">
+        <v>299</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" t="s">
+        <v>35</v>
+      </c>
+      <c r="B126" t="s">
+        <v>164</v>
+      </c>
+      <c r="C126" t="s">
+        <v>300</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" t="s">
+        <v>36</v>
+      </c>
+      <c r="B127" t="s">
+        <v>165</v>
+      </c>
+      <c r="C127" t="s">
+        <v>301</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" t="s">
+        <v>38</v>
+      </c>
+      <c r="B128" t="s">
+        <v>166</v>
+      </c>
+      <c r="C128" t="s">
+        <v>302</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" t="s">
+        <v>24</v>
+      </c>
+      <c r="B129" t="s">
         <v>167</v>
       </c>
-      <c r="D80" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E80">
+      <c r="C129" t="s">
+        <v>303</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" t="s">
+        <v>14</v>
+      </c>
+      <c r="B130" t="s">
+        <v>168</v>
+      </c>
+      <c r="C130" t="s">
+        <v>219</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" t="s">
+        <v>5</v>
+      </c>
+      <c r="B131" t="s">
+        <v>169</v>
+      </c>
+      <c r="C131" t="s">
+        <v>304</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" t="s">
+        <v>36</v>
+      </c>
+      <c r="B132" t="s">
+        <v>170</v>
+      </c>
+      <c r="C132" t="s">
+        <v>305</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" t="s">
+        <v>36</v>
+      </c>
+      <c r="B133" t="s">
+        <v>171</v>
+      </c>
+      <c r="C133" t="s">
+        <v>306</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" t="s">
+        <v>19</v>
+      </c>
+      <c r="B134" t="s">
+        <v>172</v>
+      </c>
+      <c r="C134" t="s">
+        <v>307</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" t="s">
+        <v>22</v>
+      </c>
+      <c r="B135" t="s">
+        <v>173</v>
+      </c>
+      <c r="C135" t="s">
+        <v>308</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" t="s">
+        <v>27</v>
+      </c>
+      <c r="B136" t="s">
+        <v>174</v>
+      </c>
+      <c r="C136" t="s">
+        <v>309</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" t="s">
+        <v>39</v>
+      </c>
+      <c r="B137" t="s">
+        <v>175</v>
+      </c>
+      <c r="C137" t="s">
+        <v>310</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" t="s">
+        <v>36</v>
+      </c>
+      <c r="B138" t="s">
+        <v>176</v>
+      </c>
+      <c r="C138" t="s">
+        <v>311</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" t="s">
+        <v>5</v>
+      </c>
+      <c r="B139" t="s">
+        <v>177</v>
+      </c>
+      <c r="C139" t="s">
+        <v>312</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" t="s">
+        <v>5</v>
+      </c>
+      <c r="B140" t="s">
+        <v>178</v>
+      </c>
+      <c r="C140" t="s">
+        <v>313</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E140">
         <v>1</v>
       </c>
     </row>
@@ -2866,6 +4699,67 @@
     <hyperlink ref="D78" r:id="rId77"/>
     <hyperlink ref="D79" r:id="rId78"/>
     <hyperlink ref="D80" r:id="rId79"/>
+    <hyperlink ref="D81" r:id="rId80"/>
+    <hyperlink ref="D82" r:id="rId81"/>
+    <hyperlink ref="D83" r:id="rId82"/>
+    <hyperlink ref="D84" r:id="rId83"/>
+    <hyperlink ref="D85" r:id="rId84"/>
+    <hyperlink ref="D86" r:id="rId85"/>
+    <hyperlink ref="D87" r:id="rId86"/>
+    <hyperlink ref="D88" r:id="rId87"/>
+    <hyperlink ref="D89" r:id="rId88"/>
+    <hyperlink ref="D90" r:id="rId89"/>
+    <hyperlink ref="C91" r:id="rId90" location="100DaysOfCode%20#CodeNewbie%20#webDeveloper%20#frontEnd&#10;&#10;Day%2041-%20#100daysofcode%20Challenge&#10;&#10;20/2/2023🔮every%20day%20one%20step🚶🏻‍♀️☺️&#10;&#10;Creating%20an%20Animated%20Sliding%20Menu%20Indicator%20with%20Html%20CSS%20&amp;amp;%20Javascript%20in%20two%20ways&#10;&#10;@LearnWeb3DAO%20#100DaysofCodeLW3"/>
+    <hyperlink ref="D91" r:id="rId91"/>
+    <hyperlink ref="D92" r:id="rId92"/>
+    <hyperlink ref="D93" r:id="rId93"/>
+    <hyperlink ref="D94" r:id="rId94"/>
+    <hyperlink ref="D95" r:id="rId95"/>
+    <hyperlink ref="D96" r:id="rId96"/>
+    <hyperlink ref="D97" r:id="rId97"/>
+    <hyperlink ref="D98" r:id="rId98"/>
+    <hyperlink ref="D99" r:id="rId99"/>
+    <hyperlink ref="D100" r:id="rId100"/>
+    <hyperlink ref="D101" r:id="rId101"/>
+    <hyperlink ref="D102" r:id="rId102"/>
+    <hyperlink ref="D103" r:id="rId103"/>
+    <hyperlink ref="D104" r:id="rId104"/>
+    <hyperlink ref="D105" r:id="rId105"/>
+    <hyperlink ref="D106" r:id="rId106"/>
+    <hyperlink ref="D107" r:id="rId107"/>
+    <hyperlink ref="D108" r:id="rId108"/>
+    <hyperlink ref="D109" r:id="rId109"/>
+    <hyperlink ref="D110" r:id="rId110"/>
+    <hyperlink ref="D111" r:id="rId111"/>
+    <hyperlink ref="D112" r:id="rId112"/>
+    <hyperlink ref="D113" r:id="rId113"/>
+    <hyperlink ref="D114" r:id="rId114"/>
+    <hyperlink ref="D115" r:id="rId115"/>
+    <hyperlink ref="D116" r:id="rId116"/>
+    <hyperlink ref="D117" r:id="rId117"/>
+    <hyperlink ref="D118" r:id="rId118"/>
+    <hyperlink ref="D119" r:id="rId119"/>
+    <hyperlink ref="D120" r:id="rId120"/>
+    <hyperlink ref="D121" r:id="rId121"/>
+    <hyperlink ref="D122" r:id="rId122"/>
+    <hyperlink ref="D123" r:id="rId123"/>
+    <hyperlink ref="D124" r:id="rId124"/>
+    <hyperlink ref="D125" r:id="rId125"/>
+    <hyperlink ref="D126" r:id="rId126"/>
+    <hyperlink ref="D127" r:id="rId127"/>
+    <hyperlink ref="D128" r:id="rId128"/>
+    <hyperlink ref="D129" r:id="rId129"/>
+    <hyperlink ref="D130" r:id="rId130"/>
+    <hyperlink ref="D131" r:id="rId131"/>
+    <hyperlink ref="D132" r:id="rId132"/>
+    <hyperlink ref="D133" r:id="rId133"/>
+    <hyperlink ref="D134" r:id="rId134"/>
+    <hyperlink ref="D135" r:id="rId135"/>
+    <hyperlink ref="D136" r:id="rId136"/>
+    <hyperlink ref="D137" r:id="rId137"/>
+    <hyperlink ref="D138" r:id="rId138"/>
+    <hyperlink ref="D139" r:id="rId139"/>
+    <hyperlink ref="D140" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
